--- a/data/trending_integrated_20260915_10.xlsx
+++ b/data/trending_integrated_20260915_10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z19"/>
+  <dimension ref="A1:Z20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -567,24 +567,24 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>11160</v>
+        <v>10970</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+20.39%</t>
+          <t>'+18.34%</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>-0.06</v>
       </c>
       <c r="E2" t="n">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="F2" t="n">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="G2" t="n">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="H2" t="n">
         <v>1.19</v>
@@ -610,7 +610,7 @@
         <v>1.25</v>
       </c>
       <c r="O2" t="n">
-        <v>102053402900</v>
+        <v>108226300530</v>
       </c>
       <c r="P2" t="n">
         <v>25050</v>
@@ -655,31 +655,31 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>JW신약</t>
+          <t>한국첨단소재</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3650</v>
+        <v>2955</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+7.35%</t>
+          <t>'+14.31%</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.12</v>
+        <v>1.34</v>
       </c>
       <c r="E3" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F3" t="n">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="G3" t="n">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="H3" t="n">
-        <v>0.83</v>
+        <v>1.34</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -687,51 +687,51 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>3400</v>
+        <v>2585</v>
       </c>
       <c r="K3" t="n">
-        <v>3450</v>
+        <v>2725</v>
       </c>
       <c r="L3" t="n">
-        <v>4080</v>
+        <v>3200</v>
       </c>
       <c r="M3" t="n">
-        <v>3445</v>
+        <v>2690</v>
       </c>
       <c r="N3" t="n">
-        <v>0.71</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>124865013925</v>
+        <v>57405979800</v>
       </c>
       <c r="P3" t="n">
-        <v>4335</v>
+        <v>5100</v>
       </c>
       <c r="Q3" t="n">
-        <v>1246</v>
+        <v>966</v>
       </c>
       <c r="R3" t="n">
-        <v>59000</v>
+        <v>-374000</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>종목에 대한 긍정적, 부정적 의견 혼재. 단기 트레이딩 및 급등 가능성에 대한 기대와 우려 공존.</t>
+          <t>미국 기업과 594억 공급 계약 체결. 세계 최초 타이틀 및 AI 발전 수혜 기대. 프로그램 매수세 유입.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.1</v>
+        <v>0.6</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['단타', '급등', '대장주']</t>
+          <t>['공급 계약', 'AI', '세계 최초']</t>
         </is>
       </c>
       <c r="X3" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
@@ -740,77 +740,77 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>067290</t>
+          <t>062970</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>후성</t>
+          <t>JW신약</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>14870</v>
+        <v>3650</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+5.39%</t>
+          <t>'+7.35%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.06</v>
+        <v>0.12</v>
       </c>
       <c r="E4" t="n">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="F4" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G4" t="n">
-        <v>86</v>
+        <v>136</v>
       </c>
       <c r="H4" t="n">
-        <v>10.75</v>
+        <v>0.83</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>14110</v>
+        <v>3400</v>
       </c>
       <c r="K4" t="n">
-        <v>14110</v>
+        <v>3450</v>
       </c>
       <c r="L4" t="n">
-        <v>15250</v>
+        <v>4080</v>
       </c>
       <c r="M4" t="n">
-        <v>13400</v>
+        <v>3445</v>
       </c>
       <c r="N4" t="n">
-        <v>10.69</v>
+        <v>0.71</v>
       </c>
       <c r="O4" t="n">
-        <v>74822300910</v>
+        <v>127177798122</v>
       </c>
       <c r="P4" t="n">
-        <v>23550</v>
+        <v>4335</v>
       </c>
       <c r="Q4" t="n">
-        <v>5700</v>
+        <v>1246</v>
       </c>
       <c r="R4" t="n">
-        <v>-124000</v>
+        <v>59000</v>
       </c>
       <c r="S4" t="n">
-        <v>45000</v>
+        <v>0</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>거래량 증가 및 주가 상승에 대한 기대감 표출. 공매도 관련 언급.</t>
+          <t>프로그램 매수세 유입 및 외인 매수 전환. 물량 교체 후 주가 상승 기대감.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
@@ -819,11 +819,11 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['거래량', '공매도', '주가상승']</t>
+          <t>['프로그램', '외인', '물량']</t>
         </is>
       </c>
       <c r="X4" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
@@ -832,38 +832,38 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>093370</t>
+          <t>067290</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>SK이노베이션</t>
+          <t>후성</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>142000</v>
+        <v>14810</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+3.88%</t>
+          <t>'+4.96%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="E5" t="n">
-        <v>97</v>
+        <v>43</v>
       </c>
       <c r="F5" t="n">
-        <v>50</v>
+        <v>33</v>
       </c>
       <c r="G5" t="n">
-        <v>214</v>
+        <v>88</v>
       </c>
       <c r="H5" t="n">
-        <v>15.81</v>
+        <v>10.75</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -871,47 +871,47 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>136700</v>
+        <v>14110</v>
       </c>
       <c r="K5" t="n">
-        <v>139500</v>
+        <v>14110</v>
       </c>
       <c r="L5" t="n">
-        <v>144100</v>
+        <v>15250</v>
       </c>
       <c r="M5" t="n">
-        <v>138200</v>
+        <v>13400</v>
       </c>
       <c r="N5" t="n">
-        <v>15.76</v>
+        <v>10.69</v>
       </c>
       <c r="O5" t="n">
-        <v>65059954050</v>
+        <v>78067591045</v>
       </c>
       <c r="P5" t="n">
-        <v>164700</v>
+        <v>23550</v>
       </c>
       <c r="Q5" t="n">
-        <v>87700</v>
+        <v>5700</v>
       </c>
       <c r="R5" t="n">
-        <v>38000</v>
+        <v>-124000</v>
       </c>
       <c r="S5" t="n">
-        <v>5000</v>
+        <v>45000</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>합병 철회 가능성 및 정규장 시작 시 주가 하락 우려. 영업이익 10조 언급과 관련한 불확실성.</t>
+          <t>거래량 증가와 함께 주가 상승 추세. 공매도 세력과의 동향 주시 및 기관 매수세 기대.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['합병', '영업이익', '주가 하락']</t>
+          <t>['거래량', '공매도', '기관']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -924,38 +924,38 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>096770</t>
+          <t>093370</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>광전자</t>
+          <t>SK이노베이션</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>10660</v>
+        <v>142700</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+3.80%</t>
+          <t>'+4.39%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.26</v>
+        <v>0.05</v>
       </c>
       <c r="E6" t="n">
-        <v>85</v>
+        <v>101</v>
       </c>
       <c r="F6" t="n">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="G6" t="n">
-        <v>237</v>
+        <v>221</v>
       </c>
       <c r="H6" t="n">
-        <v>17.93</v>
+        <v>15.81</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -963,51 +963,51 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>10270</v>
+        <v>136700</v>
       </c>
       <c r="K6" t="n">
-        <v>11000</v>
+        <v>139500</v>
       </c>
       <c r="L6" t="n">
-        <v>11650</v>
+        <v>144100</v>
       </c>
       <c r="M6" t="n">
-        <v>10010</v>
+        <v>138200</v>
       </c>
       <c r="N6" t="n">
-        <v>17.67</v>
+        <v>15.76</v>
       </c>
       <c r="O6" t="n">
-        <v>222649653925</v>
+        <v>69860911350</v>
       </c>
       <c r="P6" t="n">
-        <v>22450</v>
+        <v>164700</v>
       </c>
       <c r="Q6" t="n">
-        <v>1760</v>
+        <v>87700</v>
       </c>
       <c r="R6" t="n">
-        <v>303000</v>
+        <v>38000</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>AI 관련 미국 광통신주 급등에 따른 기대감 반영. 기타법인 순매수 확인.</t>
+          <t>합병 철회 가능성 및 정규장 시작 시 주가 하락 우려. 영업이익 10조 언급과 관련한 불확실성.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['광통신', 'AI', '미국주식']</t>
+          <t>['합병', '영업이익', '주가 하락']</t>
         </is>
       </c>
       <c r="X6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
@@ -1016,90 +1016,90 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>017900</t>
+          <t>096770</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>HLB</t>
+          <t>광전자</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>31100</v>
+        <v>10600</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+2.47%</t>
+          <t>'+3.21%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-0.05</v>
+        <v>0.26</v>
       </c>
       <c r="E7" t="n">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="F7" t="n">
         <v>72</v>
       </c>
       <c r="G7" t="n">
-        <v>447</v>
+        <v>243</v>
       </c>
       <c r="H7" t="n">
-        <v>17.5</v>
+        <v>17.93</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>30350</v>
+        <v>10270</v>
       </c>
       <c r="K7" t="n">
-        <v>30250</v>
+        <v>11000</v>
       </c>
       <c r="L7" t="n">
-        <v>31500</v>
+        <v>11650</v>
       </c>
       <c r="M7" t="n">
-        <v>30250</v>
+        <v>10010</v>
       </c>
       <c r="N7" t="n">
-        <v>17.55</v>
+        <v>17.67</v>
       </c>
       <c r="O7" t="n">
-        <v>4112813050</v>
+        <v>232665610515</v>
       </c>
       <c r="P7" t="n">
-        <v>69200</v>
+        <v>22450</v>
       </c>
       <c r="Q7" t="n">
-        <v>24150</v>
+        <v>1760</v>
       </c>
       <c r="R7" t="n">
-        <v>19000</v>
+        <v>303000</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>리브라 담관암 FDA 승인 기대감과 제약 유증에 따른 투자 심리 위축. 주가 하락 및 회복에 대한 상반된 전망.</t>
+          <t>트럼프 AI 정책 기대감에 따른 광통신 섹터 상승 전망. 아이온큐 프리마켓 급등 및 기타법인 매수세 유입.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['담관암', 'FDA 승인', '유증']</t>
+          <t>['AI', '광통신', '트럼프']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -1108,38 +1108,38 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>028300</t>
+          <t>017900</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>흥구석유</t>
+          <t>HLB</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>14980</v>
+        <v>31100</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+2.18%</t>
+          <t>'+2.47%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-1.17</v>
+        <v>-0.05</v>
       </c>
       <c r="E8" t="n">
-        <v>111</v>
+        <v>88</v>
       </c>
       <c r="F8" t="n">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="G8" t="n">
-        <v>251</v>
+        <v>474</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1147,51 +1147,51 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>14660</v>
+        <v>30350</v>
       </c>
       <c r="K8" t="n">
-        <v>14980</v>
+        <v>30250</v>
       </c>
       <c r="L8" t="n">
-        <v>15460</v>
+        <v>31500</v>
       </c>
       <c r="M8" t="n">
-        <v>14330</v>
+        <v>30250</v>
       </c>
       <c r="N8" t="n">
-        <v>1.17</v>
+        <v>17.55</v>
       </c>
       <c r="O8" t="n">
-        <v>32004632380</v>
+        <v>4574448350</v>
       </c>
       <c r="P8" t="n">
-        <v>36200</v>
+        <v>69200</v>
       </c>
       <c r="Q8" t="n">
-        <v>8920</v>
+        <v>24150</v>
       </c>
       <c r="R8" t="n">
-        <v>-47000</v>
+        <v>19000</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>이란 사태 관련 국제유가 상승 가능성 및 중국의 원유 현물 싹쓸이 소식. 사우디 송유관 복구 지연 언급.</t>
+          <t>HLB 리보세라닙 간암 및 담관암 FDA 승인 관련 기대감과 함께, 제약 유증 및 CRL 공시로 인한 부정적 전망. 기관 및 외인 이탈 관측.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['국제유가', '이란', '원유']</t>
+          <t>['리보세라닙', 'FDA', '담관암']</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
@@ -1200,7 +1200,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>024060</t>
+          <t>028300</t>
         </is>
       </c>
     </row>
@@ -1222,13 +1222,13 @@
         <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="F9" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G9" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="H9" t="n">
         <v>0.6</v>
@@ -1254,7 +1254,7 @@
         <v>0.6</v>
       </c>
       <c r="O9" t="n">
-        <v>132671394935</v>
+        <v>134858038285</v>
       </c>
       <c r="P9" t="n">
         <v>15960</v>
@@ -1270,16 +1270,16 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>주가 조작 및 공매도 관련 부정적 언급 다수. 미프진 관련 논란.</t>
+          <t>주가 조작 의혹 및 공매도 문제로 인한 주가 하락 우려. 신약 개발 관련 불확실성.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['주가조작', '공매도', '미프진']</t>
+          <t>['주가 조작', '공매도', '신약']</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1299,31 +1299,31 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1704000</v>
+        <v>250750</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+0.41%</t>
+          <t>'+0.70%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>-0.2</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="E10" t="n">
         <v>800</v>
       </c>
       <c r="F10" t="n">
-        <v>470</v>
+        <v>476</v>
       </c>
       <c r="G10" t="n">
-        <v>2044</v>
+        <v>2194</v>
       </c>
       <c r="H10" t="n">
-        <v>50.27</v>
+        <v>46.57</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1331,51 +1331,51 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>1697000</v>
+        <v>249000</v>
       </c>
       <c r="K10" t="n">
-        <v>1690000</v>
+        <v>248000</v>
       </c>
       <c r="L10" t="n">
-        <v>1725000</v>
+        <v>252000</v>
       </c>
       <c r="M10" t="n">
-        <v>1685000</v>
+        <v>247500</v>
       </c>
       <c r="N10" t="n">
-        <v>50.47</v>
+        <v>46.64</v>
       </c>
       <c r="O10" t="n">
-        <v>1293494399500</v>
+        <v>728275897250</v>
       </c>
       <c r="P10" t="n">
-        <v>2987000</v>
+        <v>374500</v>
       </c>
       <c r="Q10" t="n">
-        <v>325000</v>
+        <v>75900</v>
       </c>
       <c r="R10" t="n">
-        <v>-66000</v>
+        <v>-156000</v>
       </c>
       <c r="S10" t="n">
-        <v>-53000</v>
+        <v>-305000</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>조정 후 상승 기대감. 외국인 매수세 유입 및 주가 상승 전망. 단기 급등 가능성 언급.</t>
+          <t>AI 관련 기대감 및 시장 전반의 흐름 속 삼성전자 주가 소폭 상승. 반도체 수요 감소 우려.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['반도체', '외국인수급', '주가전망']</t>
+          <t>['AI', '반도체', '수요']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>71</v>
+        <v>106</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -1384,90 +1384,90 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>흥구석유</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>250000</v>
+        <v>14760</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'+0.40%</t>
+          <t>'+0.68%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-1.17</v>
       </c>
       <c r="E11" t="n">
-        <v>800</v>
+        <v>112</v>
       </c>
       <c r="F11" t="n">
-        <v>468</v>
+        <v>75</v>
       </c>
       <c r="G11" t="n">
-        <v>2263</v>
+        <v>258</v>
       </c>
       <c r="H11" t="n">
-        <v>46.57</v>
+        <v>0</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>249000</v>
+        <v>14660</v>
       </c>
       <c r="K11" t="n">
-        <v>248000</v>
+        <v>14980</v>
       </c>
       <c r="L11" t="n">
-        <v>252000</v>
+        <v>15460</v>
       </c>
       <c r="M11" t="n">
-        <v>247500</v>
+        <v>14330</v>
       </c>
       <c r="N11" t="n">
-        <v>46.64</v>
+        <v>1.17</v>
       </c>
       <c r="O11" t="n">
-        <v>695016627250</v>
+        <v>32840436390</v>
       </c>
       <c r="P11" t="n">
-        <v>374500</v>
+        <v>36200</v>
       </c>
       <c r="Q11" t="n">
-        <v>75900</v>
+        <v>8920</v>
       </c>
       <c r="R11" t="n">
-        <v>-156000</v>
+        <v>-47000</v>
       </c>
       <c r="S11" t="n">
-        <v>-305000</v>
+        <v>0</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>국내 증시 반등 기대감 속 삼성전자 주가 변동성 예상. 메모리 반도체 수요 관련 언급.</t>
+          <t>이란 관련 지정학적 리스크 및 국제유가 상승으로 인한 기대감. 그러나 실제 주가 움직임은 장난질에 그치고 있으며, 유가 상승에도 불구하고 하락하는 모습.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['반도체', '주가전망', '국채금리']</t>
+          <t>['국제유가', '이란', '지정학적 리스크']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>106</v>
+        <v>5</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -1476,90 +1476,90 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>024060</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>샌즈랩</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>18750</v>
+        <v>6940</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-0.05%</t>
+          <t>'+0.58%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>-0.02</v>
+        <v>-0.97</v>
       </c>
       <c r="E12" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="F12" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="G12" t="n">
-        <v>145</v>
+        <v>97</v>
       </c>
       <c r="H12" t="n">
-        <v>10.53</v>
+        <v>0.7</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>18760</v>
+        <v>6900</v>
       </c>
       <c r="K12" t="n">
-        <v>18440</v>
+        <v>7500</v>
       </c>
       <c r="L12" t="n">
-        <v>18750</v>
+        <v>8190</v>
       </c>
       <c r="M12" t="n">
-        <v>18120</v>
+        <v>6730</v>
       </c>
       <c r="N12" t="n">
-        <v>10.55</v>
+        <v>1.67</v>
       </c>
       <c r="O12" t="n">
-        <v>19709177935</v>
+        <v>27500787800</v>
       </c>
       <c r="P12" t="n">
-        <v>40350</v>
+        <v>10360</v>
       </c>
       <c r="Q12" t="n">
-        <v>3320</v>
+        <v>2965</v>
       </c>
       <c r="R12" t="n">
-        <v>69000</v>
+        <v>35000</v>
       </c>
       <c r="S12" t="n">
-        <v>-6000</v>
+        <v>0</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>대차해지 운동 관련 언급 다수. 해외 건설 사업 및 AI 관련 기대감 존재하나, 주가 하락 및 불안정성 우려.</t>
+          <t>미국 보안주 강세와 네이버클라우드 컨소시엄 소속이라는 점을 바탕으로 594억 공급계약 및 양자암호 관련 호재 기대. 단일가 예고 공시로 인한 상승 제한 가능성.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['대차해지', '해외건설', 'AI']</t>
+          <t>['사이버보안', '양자암호', '공급계약']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
@@ -1568,90 +1568,90 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>411080</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>샌즈랩</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>6870</v>
+        <v>1706500</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-0.43%</t>
+          <t>'+0.56%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>-0.97</v>
+        <v>-0.2</v>
       </c>
       <c r="E13" t="n">
-        <v>41</v>
+        <v>800</v>
       </c>
       <c r="F13" t="n">
-        <v>25</v>
+        <v>460</v>
       </c>
       <c r="G13" t="n">
-        <v>96</v>
+        <v>2021</v>
       </c>
       <c r="H13" t="n">
-        <v>0.7</v>
+        <v>50.27</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>6900</v>
+        <v>1697000</v>
       </c>
       <c r="K13" t="n">
-        <v>7500</v>
+        <v>1690000</v>
       </c>
       <c r="L13" t="n">
-        <v>8190</v>
+        <v>1725000</v>
       </c>
       <c r="M13" t="n">
-        <v>6730</v>
+        <v>1685000</v>
       </c>
       <c r="N13" t="n">
-        <v>1.67</v>
+        <v>50.47</v>
       </c>
       <c r="O13" t="n">
-        <v>26918897380</v>
+        <v>1391548537000</v>
       </c>
       <c r="P13" t="n">
-        <v>10360</v>
+        <v>2987000</v>
       </c>
       <c r="Q13" t="n">
-        <v>2965</v>
+        <v>325000</v>
       </c>
       <c r="R13" t="n">
-        <v>35000</v>
+        <v>-66000</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>-53000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>미국 보안주 강세 및 양자암호 관련 트럼프 행정명령 발표에 따른 단기 테마 기대감. 미국 기업과의 594억 공급 계약 언급.</t>
+          <t>나스닥 선물 흐름 호조 및 조정 국면 종료 기대감. 외국인 매수 동향 주시.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['보안주', '양자암호', '공급계약']</t>
+          <t>['나스닥', '조정', '외국인']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>2</v>
+        <v>71</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
@@ -1660,38 +1660,38 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>411080</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>한미반도체</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>224000</v>
+        <v>18800</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-0.44%</t>
+          <t>'+0.21%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0.15</v>
+        <v>-0.02</v>
       </c>
       <c r="E14" t="n">
-        <v>107</v>
+        <v>43</v>
       </c>
       <c r="F14" t="n">
-        <v>61</v>
+        <v>30</v>
       </c>
       <c r="G14" t="n">
-        <v>489</v>
+        <v>161</v>
       </c>
       <c r="H14" t="n">
-        <v>7.2</v>
+        <v>10.53</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1699,51 +1699,51 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>225000</v>
+        <v>18760</v>
       </c>
       <c r="K14" t="n">
-        <v>228500</v>
+        <v>18440</v>
       </c>
       <c r="L14" t="n">
-        <v>229000</v>
+        <v>19060</v>
       </c>
       <c r="M14" t="n">
-        <v>219500</v>
+        <v>18120</v>
       </c>
       <c r="N14" t="n">
-        <v>7.05</v>
+        <v>10.55</v>
       </c>
       <c r="O14" t="n">
-        <v>53309732750</v>
+        <v>26705180425</v>
       </c>
       <c r="P14" t="n">
-        <v>426000</v>
+        <v>40350</v>
       </c>
       <c r="Q14" t="n">
-        <v>89500</v>
+        <v>3320</v>
       </c>
       <c r="R14" t="n">
-        <v>-102000</v>
+        <v>69000</v>
       </c>
       <c r="S14" t="n">
-        <v>-2000</v>
+        <v>-6000</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>일론 머스크의 테슬라 자회사 테라팹에 패키징 장비 공급 뉴스 기반 반등 기대. 공매도 관련 언급.</t>
+          <t>대차해지 운동을 통한 주가 부양 기대감. AI 관련주 편입 가능성 및 해외 건설 수주.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['테라팹', '패키징 장비', '공매도']</t>
+          <t>['대차해지', 'AI', '건설']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
@@ -1752,38 +1752,38 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>042700</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>LG디스플레이</t>
+          <t>한미반도체</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>8780</v>
+        <v>224500</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-0.79%</t>
+          <t>'-0.22%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>0.15</v>
       </c>
       <c r="E15" t="n">
-        <v>51</v>
+        <v>110</v>
       </c>
       <c r="F15" t="n">
-        <v>33</v>
+        <v>62</v>
       </c>
       <c r="G15" t="n">
-        <v>190</v>
+        <v>503</v>
       </c>
       <c r="H15" t="n">
-        <v>27.16</v>
+        <v>7.2</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1791,51 +1791,51 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>8850</v>
+        <v>225000</v>
       </c>
       <c r="K15" t="n">
-        <v>8750</v>
+        <v>228500</v>
       </c>
       <c r="L15" t="n">
-        <v>8820</v>
+        <v>229000</v>
       </c>
       <c r="M15" t="n">
-        <v>8670</v>
+        <v>219500</v>
       </c>
       <c r="N15" t="n">
-        <v>27.16</v>
+        <v>7.05</v>
       </c>
       <c r="O15" t="n">
-        <v>10497677370</v>
+        <v>54875565000</v>
       </c>
       <c r="P15" t="n">
-        <v>17950</v>
+        <v>426000</v>
       </c>
       <c r="Q15" t="n">
-        <v>8120</v>
+        <v>89500</v>
       </c>
       <c r="R15" t="n">
-        <v>-427000</v>
+        <v>-102000</v>
       </c>
       <c r="S15" t="n">
-        <v>-11000</v>
+        <v>-2000</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>적자 지속 및 목표주가 하향 조정 관련 부정적 언급. 경영진 사퇴 요구.</t>
+          <t>머스크 테라팹 공급 계약 관련 단독 보도 및 나스닥 반등으로 인한 상승 기대감. 공매도 세력에 대한 언급과 함께 주주환원 정책 요구.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0.2</v>
+        <v>0.6</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['적자', '목표주가', '경영진']</t>
+          <t>['패키징장비', '테라팹', '공매도']</t>
         </is>
       </c>
       <c r="X15" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
@@ -1844,38 +1844,38 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>034220</t>
+          <t>042700</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>LG디스플레이</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>85450</v>
+        <v>8790</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'-1.78%</t>
+          <t>'-0.68%</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>-0.11</v>
+        <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>105</v>
+        <v>59</v>
       </c>
       <c r="F16" t="n">
-        <v>65</v>
+        <v>36</v>
       </c>
       <c r="G16" t="n">
-        <v>487</v>
+        <v>196</v>
       </c>
       <c r="H16" t="n">
-        <v>23.45</v>
+        <v>27.16</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1883,51 +1883,51 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>87000</v>
+        <v>8850</v>
       </c>
       <c r="K16" t="n">
-        <v>86200</v>
+        <v>8750</v>
       </c>
       <c r="L16" t="n">
-        <v>86500</v>
+        <v>8820</v>
       </c>
       <c r="M16" t="n">
-        <v>85000</v>
+        <v>8670</v>
       </c>
       <c r="N16" t="n">
-        <v>23.56</v>
+        <v>27.16</v>
       </c>
       <c r="O16" t="n">
-        <v>50074708500</v>
+        <v>11638229705</v>
       </c>
       <c r="P16" t="n">
-        <v>139200</v>
+        <v>17950</v>
       </c>
       <c r="Q16" t="n">
-        <v>57000</v>
+        <v>8120</v>
       </c>
       <c r="R16" t="n">
-        <v>-164000</v>
+        <v>-427000</v>
       </c>
       <c r="S16" t="n">
-        <v>-62000</v>
+        <v>-11000</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>미국 엑스에너지 급등 및 원전 관련 ETF 출시 소식으로 인한 상승 기대감. 중앙아시아 5개국 협력 가능성 언급.</t>
+          <t>적자 지속 및 목표주가 하향 조정 관련 부정적 언급. 경영진 사퇴 요구.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['원전', '엑스에너지', 'ETF']</t>
+          <t>['적자', '목표주가', '경영진']</t>
         </is>
       </c>
       <c r="X16" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
@@ -1936,7 +1936,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>034220</t>
         </is>
       </c>
     </row>
@@ -1947,24 +1947,24 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>14090</v>
+        <v>14240</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'-2.76%</t>
+          <t>'-1.73%</t>
         </is>
       </c>
       <c r="D17" t="n">
         <v>-0.08</v>
       </c>
       <c r="E17" t="n">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="F17" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G17" t="n">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="H17" t="n">
         <v>1.8</v>
@@ -1990,7 +1990,7 @@
         <v>1.88</v>
       </c>
       <c r="O17" t="n">
-        <v>32258477005</v>
+        <v>33956077550</v>
       </c>
       <c r="P17" t="n">
         <v>31500</v>
@@ -2006,16 +2006,16 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>머니투데이 방송 홍보에도 주가 하락. 대선 변수 및 FOMC 금리 등 불확실성 언급.</t>
+          <t>머니투데이 방송 홍보 언급 있으나, 미증시 하락 및 FOMC 금리, 유가 등 변수로 인한 하락세. 외국인 보유율이 낮다는 점은 긍정적 요인.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['홍보', '대선', 'FOMC']</t>
+          <t>['광통신', 'FOMC', '유가']</t>
         </is>
       </c>
       <c r="X17" t="n">
@@ -2035,31 +2035,31 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>삼성중공업</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>21350</v>
+        <v>85450</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'-3.39%</t>
+          <t>'-1.78%</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>0.09</v>
+        <v>-0.11</v>
       </c>
       <c r="E18" t="n">
-        <v>74</v>
+        <v>119</v>
       </c>
       <c r="F18" t="n">
-        <v>47</v>
+        <v>72</v>
       </c>
       <c r="G18" t="n">
-        <v>177</v>
+        <v>511</v>
       </c>
       <c r="H18" t="n">
-        <v>28.9</v>
+        <v>23.45</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -2067,51 +2067,51 @@
         </is>
       </c>
       <c r="J18" t="n">
-        <v>22100</v>
+        <v>87000</v>
       </c>
       <c r="K18" t="n">
-        <v>21850</v>
+        <v>86200</v>
       </c>
       <c r="L18" t="n">
-        <v>21850</v>
+        <v>86500</v>
       </c>
       <c r="M18" t="n">
-        <v>21150</v>
+        <v>85000</v>
       </c>
       <c r="N18" t="n">
-        <v>28.81</v>
+        <v>23.56</v>
       </c>
       <c r="O18" t="n">
-        <v>25559571850</v>
+        <v>53849699900</v>
       </c>
       <c r="P18" t="n">
-        <v>35350</v>
+        <v>139200</v>
       </c>
       <c r="Q18" t="n">
-        <v>18440</v>
+        <v>57000</v>
       </c>
       <c r="R18" t="n">
-        <v>-616000</v>
+        <v>-164000</v>
       </c>
       <c r="S18" t="n">
-        <v>-49000</v>
+        <v>-62000</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>12억 달러 수주 공시 기반 주가 상승 기대감 있으나, 단기 하락 및 불안정한 투심. 악질 주포 및 신뢰도 문제 지적.</t>
+          <t>미국 엑스에너지 급등 및 원전 관련 ETF 출시 소식으로 인한 상승 기대감. 중앙아시아 5개국 협력 가능성 언급.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['수주', '공시', '투심']</t>
+          <t>['원전', '엑스에너지', 'ETF']</t>
         </is>
       </c>
       <c r="X18" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
@@ -2120,97 +2120,189 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>010140</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>빛과전자</t>
+          <t>삼성중공업</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>4160</v>
+        <v>21300</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'-3.82%</t>
+          <t>'-3.62%</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>0.18</v>
+        <v>0.09</v>
       </c>
       <c r="E19" t="n">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="F19" t="n">
-        <v>29</v>
+        <v>53</v>
       </c>
       <c r="G19" t="n">
-        <v>109</v>
+        <v>190</v>
       </c>
       <c r="H19" t="n">
-        <v>0.77</v>
+        <v>28.9</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>4325</v>
+        <v>22100</v>
       </c>
       <c r="K19" t="n">
-        <v>4325</v>
+        <v>21850</v>
       </c>
       <c r="L19" t="n">
-        <v>4415</v>
+        <v>21850</v>
       </c>
       <c r="M19" t="n">
-        <v>4050</v>
+        <v>21150</v>
       </c>
       <c r="N19" t="n">
-        <v>0.59</v>
+        <v>28.81</v>
       </c>
       <c r="O19" t="n">
-        <v>38166511859</v>
+        <v>26880808900</v>
       </c>
       <c r="P19" t="n">
-        <v>8100</v>
+        <v>35350</v>
       </c>
       <c r="Q19" t="n">
-        <v>592</v>
+        <v>18440</v>
       </c>
       <c r="R19" t="n">
-        <v>95000</v>
+        <v>-616000</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>-49000</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>594억 규모 공급 계약에 대한 긍정적 전망과 광통신/5G 관련주 동반 하락 우려. 주가 움직임 둔감 및 기대 이하 실망감.</t>
+          <t>12억 달러 규모 수주 공시 확인. 금투, 투신, 연기금 등 기관 매도세 및 주포 악질 행태 경고.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
       <c r="V19" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>['수주', '기관', '주포']</t>
+        </is>
+      </c>
+      <c r="X19" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>010140</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>빛과전자</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>4162</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>'-3.77%</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="E20" t="n">
+        <v>42</v>
+      </c>
+      <c r="F20" t="n">
+        <v>31</v>
+      </c>
+      <c r="G20" t="n">
+        <v>119</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="J20" t="n">
+        <v>4325</v>
+      </c>
+      <c r="K20" t="n">
+        <v>4325</v>
+      </c>
+      <c r="L20" t="n">
+        <v>4415</v>
+      </c>
+      <c r="M20" t="n">
+        <v>4050</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="O20" t="n">
+        <v>40214815813</v>
+      </c>
+      <c r="P20" t="n">
+        <v>8100</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>592</v>
+      </c>
+      <c r="R20" t="n">
+        <v>95000</v>
+      </c>
+      <c r="S20" t="n">
+        <v>0</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>미국 기업과 594억 공급 계약 호재. 광통신 및 5G 관련주와 비교되며 주가 상승 기대. 광전자 대비 낮은 상승률.</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr"/>
+      <c r="V20" t="n">
         <v>0.3</v>
       </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>['공급계약', '광통신', '5G']</t>
-        </is>
-      </c>
-      <c r="X19" t="n">
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>['공급 계약', '광통신', '5G']</t>
+        </is>
+      </c>
+      <c r="X20" t="n">
         <v>6</v>
       </c>
-      <c r="Y19" t="inlineStr">
+      <c r="Y20" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
+      <c r="Z20" t="inlineStr">
         <is>
           <t>069540</t>
         </is>

--- a/data/trending_integrated_20260915_10.xlsx
+++ b/data/trending_integrated_20260915_10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z20"/>
+  <dimension ref="A1:Z21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -567,24 +567,24 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>10970</v>
+        <v>10920</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+18.34%</t>
+          <t>'+17.80%</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>-0.06</v>
       </c>
       <c r="E2" t="n">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="F2" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="G2" t="n">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="H2" t="n">
         <v>1.19</v>
@@ -610,7 +610,7 @@
         <v>1.25</v>
       </c>
       <c r="O2" t="n">
-        <v>108226300530</v>
+        <v>112502958960</v>
       </c>
       <c r="P2" t="n">
         <v>25050</v>
@@ -626,16 +626,16 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>장기지속형 주사제 기술 특허 등록 및 노보노디스크 협력 기대감. 품절주 및 목표가 30만 언급.</t>
+          <t>세계 최초 면역조절 펩타이드 장기지속형 제제 기술 특허 등록 및 품절주 관련 언급. 다만, 급등락 및 일부 부정적 의견 혼재.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['장기지속형주사제', '펩타이드', '특허']</t>
+          <t>['품절주', '특허 등록', '장기지속형']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2955</v>
+        <v>2915</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+14.31%</t>
+          <t>'+12.77%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>1.34</v>
       </c>
       <c r="E3" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F3" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G3" t="n">
-        <v>91</v>
+        <v>110</v>
       </c>
       <c r="H3" t="n">
         <v>1.34</v>
@@ -702,7 +702,7 @@
         <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>57405979800</v>
+        <v>58743564785</v>
       </c>
       <c r="P3" t="n">
         <v>5100</v>
@@ -718,16 +718,16 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>미국 기업과 594억 공급 계약 체결. 세계 최초 타이틀 및 AI 발전 수혜 기대. 프로그램 매수세 유입.</t>
+          <t>미국 기업과의 594억 규모 공급 계약 체결 및 세계 최초 타이틀 관련 호재. AI 발전 수혜 기대감.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['공급 계약', 'AI', '세계 최초']</t>
+          <t>['공급계약', 'AI', '세계최초']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -747,70 +747,70 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>JW신약</t>
+          <t>현대제철</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3650</v>
+        <v>36000</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+7.35%</t>
+          <t>'+9.09%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.12</v>
+        <v>-0.13</v>
       </c>
       <c r="E4" t="n">
-        <v>50</v>
+        <v>41</v>
       </c>
       <c r="F4" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="G4" t="n">
-        <v>136</v>
+        <v>161</v>
       </c>
       <c r="H4" t="n">
-        <v>0.83</v>
+        <v>14.93</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>3400</v>
+        <v>33000</v>
       </c>
       <c r="K4" t="n">
-        <v>3450</v>
+        <v>32750</v>
       </c>
       <c r="L4" t="n">
-        <v>4080</v>
+        <v>37200</v>
       </c>
       <c r="M4" t="n">
-        <v>3445</v>
+        <v>32750</v>
       </c>
       <c r="N4" t="n">
-        <v>0.71</v>
+        <v>15.06</v>
       </c>
       <c r="O4" t="n">
-        <v>127177798122</v>
+        <v>32114228200</v>
       </c>
       <c r="P4" t="n">
-        <v>4335</v>
+        <v>50400</v>
       </c>
       <c r="Q4" t="n">
-        <v>1246</v>
+        <v>23650</v>
       </c>
       <c r="R4" t="n">
-        <v>59000</v>
+        <v>126000</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>프로그램 매수세 유입 및 외인 매수 전환. 물량 교체 후 주가 상승 기대감.</t>
+          <t>초장기 상승 추세 및 저 PBR 이슈에 따른 120일선 돌파. 한국거래소의 저평가 기업 정책 기대감.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
@@ -819,11 +819,11 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['프로그램', '외인', '물량']</t>
+          <t>['저PBR', '120일선', '정배열']</t>
         </is>
       </c>
       <c r="X4" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
@@ -832,90 +832,90 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>067290</t>
+          <t>004020</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>후성</t>
+          <t>JW신약</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>14810</v>
+        <v>3695</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+4.96%</t>
+          <t>'+8.68%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.06</v>
+        <v>0.12</v>
       </c>
       <c r="E5" t="n">
-        <v>43</v>
+        <v>56</v>
       </c>
       <c r="F5" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="G5" t="n">
-        <v>88</v>
+        <v>150</v>
       </c>
       <c r="H5" t="n">
-        <v>10.75</v>
+        <v>0.83</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>14110</v>
+        <v>3400</v>
       </c>
       <c r="K5" t="n">
-        <v>14110</v>
+        <v>3450</v>
       </c>
       <c r="L5" t="n">
-        <v>15250</v>
+        <v>4080</v>
       </c>
       <c r="M5" t="n">
-        <v>13400</v>
+        <v>3445</v>
       </c>
       <c r="N5" t="n">
-        <v>10.69</v>
+        <v>0.71</v>
       </c>
       <c r="O5" t="n">
-        <v>78067591045</v>
+        <v>129630417308</v>
       </c>
       <c r="P5" t="n">
-        <v>23550</v>
+        <v>4335</v>
       </c>
       <c r="Q5" t="n">
-        <v>5700</v>
+        <v>1246</v>
       </c>
       <c r="R5" t="n">
-        <v>-124000</v>
+        <v>59000</v>
       </c>
       <c r="S5" t="n">
-        <v>45000</v>
+        <v>0</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>거래량 증가와 함께 주가 상승 추세. 공매도 세력과의 동향 주시 및 기관 매수세 기대.</t>
+          <t>프로그램 매도 후 외국인 순매수 전환 및 4천원 안착 시도. 삼익제약과의 비교를 통한 대장주 경쟁.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['거래량', '공매도', '기관']</t>
+          <t>['외국인순매수', '프로그램', '단타']</t>
         </is>
       </c>
       <c r="X5" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
@@ -924,38 +924,38 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>093370</t>
+          <t>067290</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>SK이노베이션</t>
+          <t>후성</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>142700</v>
+        <v>14980</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+4.39%</t>
+          <t>'+6.17%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="E6" t="n">
-        <v>101</v>
+        <v>44</v>
       </c>
       <c r="F6" t="n">
-        <v>53</v>
+        <v>34</v>
       </c>
       <c r="G6" t="n">
-        <v>221</v>
+        <v>103</v>
       </c>
       <c r="H6" t="n">
-        <v>15.81</v>
+        <v>10.75</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -963,38 +963,38 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>136700</v>
+        <v>14110</v>
       </c>
       <c r="K6" t="n">
-        <v>139500</v>
+        <v>14110</v>
       </c>
       <c r="L6" t="n">
-        <v>144100</v>
+        <v>15250</v>
       </c>
       <c r="M6" t="n">
-        <v>138200</v>
+        <v>13400</v>
       </c>
       <c r="N6" t="n">
-        <v>15.76</v>
+        <v>10.69</v>
       </c>
       <c r="O6" t="n">
-        <v>69860911350</v>
+        <v>81110940195</v>
       </c>
       <c r="P6" t="n">
-        <v>164700</v>
+        <v>23550</v>
       </c>
       <c r="Q6" t="n">
-        <v>87700</v>
+        <v>5700</v>
       </c>
       <c r="R6" t="n">
-        <v>38000</v>
+        <v>-124000</v>
       </c>
       <c r="S6" t="n">
-        <v>5000</v>
+        <v>45000</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>합병 철회 가능성 및 정규장 시작 시 주가 하락 우려. 영업이익 10조 언급과 관련한 불확실성.</t>
+          <t>주요 저항선인 15000원 돌파 시도 및 거래량 증가. 주포의 의도에 따른 상승 기대감과 오전 매도 물량 출회.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['합병', '영업이익', '주가 하락']</t>
+          <t>['주포', '거래량', '저항선']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1016,38 +1016,38 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>096770</t>
+          <t>093370</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>광전자</t>
+          <t>SK이노베이션</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>10600</v>
+        <v>142100</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+3.21%</t>
+          <t>'+3.95%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.26</v>
+        <v>0.05</v>
       </c>
       <c r="E7" t="n">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="F7" t="n">
-        <v>72</v>
+        <v>57</v>
       </c>
       <c r="G7" t="n">
-        <v>243</v>
+        <v>224</v>
       </c>
       <c r="H7" t="n">
-        <v>17.93</v>
+        <v>15.81</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -1055,51 +1055,51 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>10270</v>
+        <v>136700</v>
       </c>
       <c r="K7" t="n">
-        <v>11000</v>
+        <v>139500</v>
       </c>
       <c r="L7" t="n">
-        <v>11650</v>
+        <v>144100</v>
       </c>
       <c r="M7" t="n">
-        <v>10010</v>
+        <v>138200</v>
       </c>
       <c r="N7" t="n">
-        <v>17.67</v>
+        <v>15.76</v>
       </c>
       <c r="O7" t="n">
-        <v>232665610515</v>
+        <v>73020688250</v>
       </c>
       <c r="P7" t="n">
-        <v>22450</v>
+        <v>164700</v>
       </c>
       <c r="Q7" t="n">
-        <v>1760</v>
+        <v>87700</v>
       </c>
       <c r="R7" t="n">
-        <v>303000</v>
+        <v>38000</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>트럼프 AI 정책 기대감에 따른 광통신 섹터 상승 전망. 아이온큐 프리마켓 급등 및 기타법인 매수세 유입.</t>
+          <t>합병 철회 가능성 및 정규장 시작 시 주가 하락 우려. 영업이익 10조 언급과 관련한 불확실성.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['AI', '광통신', '트럼프']</t>
+          <t>['합병', '영업이익', '주가 하락']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -1108,90 +1108,90 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>017900</t>
+          <t>096770</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>HLB</t>
+          <t>광전자</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>31100</v>
+        <v>10650</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+2.47%</t>
+          <t>'+3.70%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-0.05</v>
+        <v>0.26</v>
       </c>
       <c r="E8" t="n">
-        <v>88</v>
+        <v>101</v>
       </c>
       <c r="F8" t="n">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="G8" t="n">
-        <v>474</v>
+        <v>274</v>
       </c>
       <c r="H8" t="n">
-        <v>17.5</v>
+        <v>17.93</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>30350</v>
+        <v>10270</v>
       </c>
       <c r="K8" t="n">
-        <v>30250</v>
+        <v>11000</v>
       </c>
       <c r="L8" t="n">
-        <v>31500</v>
+        <v>11650</v>
       </c>
       <c r="M8" t="n">
-        <v>30250</v>
+        <v>10010</v>
       </c>
       <c r="N8" t="n">
-        <v>17.55</v>
+        <v>17.67</v>
       </c>
       <c r="O8" t="n">
-        <v>4574448350</v>
+        <v>237979448325</v>
       </c>
       <c r="P8" t="n">
-        <v>69200</v>
+        <v>22450</v>
       </c>
       <c r="Q8" t="n">
-        <v>24150</v>
+        <v>1760</v>
       </c>
       <c r="R8" t="n">
-        <v>19000</v>
+        <v>303000</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>HLB 리보세라닙 간암 및 담관암 FDA 승인 관련 기대감과 함께, 제약 유증 및 CRL 공시로 인한 부정적 전망. 기관 및 외인 이탈 관측.</t>
+          <t>광통신 대장주 한국첨단소재의 급등과 트럼프 AI 정책 관련 기대감. 미국 반도체 지수 하락에도 아이온큐의 양전 마감 및 기타 법인의 매수세 유입.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['리보세라닙', 'FDA', '담관암']</t>
+          <t>['광통신', 'AI', '아이온큐']</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
@@ -1200,86 +1200,86 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>028300</t>
+          <t>017900</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>현대약품</t>
+          <t>HLB</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>10120</v>
+        <v>31300</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+1.30%</t>
+          <t>'+3.13%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>-0.05</v>
       </c>
       <c r="E9" t="n">
-        <v>57</v>
+        <v>91</v>
       </c>
       <c r="F9" t="n">
-        <v>29</v>
+        <v>74</v>
       </c>
       <c r="G9" t="n">
-        <v>70</v>
+        <v>480</v>
       </c>
       <c r="H9" t="n">
-        <v>0.6</v>
+        <v>17.5</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>9990</v>
+        <v>30350</v>
       </c>
       <c r="K9" t="n">
-        <v>10110</v>
+        <v>30250</v>
       </c>
       <c r="L9" t="n">
-        <v>11390</v>
+        <v>31500</v>
       </c>
       <c r="M9" t="n">
-        <v>10040</v>
+        <v>30250</v>
       </c>
       <c r="N9" t="n">
-        <v>0.6</v>
+        <v>17.55</v>
       </c>
       <c r="O9" t="n">
-        <v>134858038285</v>
+        <v>5183884375</v>
       </c>
       <c r="P9" t="n">
-        <v>15960</v>
+        <v>69200</v>
       </c>
       <c r="Q9" t="n">
-        <v>3500</v>
+        <v>24150</v>
       </c>
       <c r="R9" t="n">
-        <v>220000</v>
+        <v>19000</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>주가 조작 의혹 및 공매도 문제로 인한 주가 하락 우려. 신약 개발 관련 불확실성.</t>
+          <t>HLB 리보세라닙 간암 및 담관암 FDA 승인 관련 기대감과 함께, 제약 유증 및 CRL 공시로 인한 부정적 전망. 기관 및 외인 이탈 관측.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.1</v>
+        <v>0.4</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['주가 조작', '공매도', '신약']</t>
+          <t>['리보세라닙', 'FDA', '담관암']</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1292,38 +1292,38 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>004310</t>
+          <t>028300</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>현대약품</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>250750</v>
+        <v>10130</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+0.70%</t>
+          <t>'+1.40%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>800</v>
+        <v>59</v>
       </c>
       <c r="F10" t="n">
-        <v>476</v>
+        <v>33</v>
       </c>
       <c r="G10" t="n">
-        <v>2194</v>
+        <v>72</v>
       </c>
       <c r="H10" t="n">
-        <v>46.57</v>
+        <v>0.6</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1331,51 +1331,51 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>249000</v>
+        <v>9990</v>
       </c>
       <c r="K10" t="n">
-        <v>248000</v>
+        <v>10110</v>
       </c>
       <c r="L10" t="n">
-        <v>252000</v>
+        <v>11390</v>
       </c>
       <c r="M10" t="n">
-        <v>247500</v>
+        <v>10040</v>
       </c>
       <c r="N10" t="n">
-        <v>46.64</v>
+        <v>0.6</v>
       </c>
       <c r="O10" t="n">
-        <v>728275897250</v>
+        <v>137462128065</v>
       </c>
       <c r="P10" t="n">
-        <v>374500</v>
+        <v>15960</v>
       </c>
       <c r="Q10" t="n">
-        <v>75900</v>
+        <v>3500</v>
       </c>
       <c r="R10" t="n">
-        <v>-156000</v>
+        <v>220000</v>
       </c>
       <c r="S10" t="n">
-        <v>-305000</v>
+        <v>0</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>AI 관련 기대감 및 시장 전반의 흐름 속 삼성전자 주가 소폭 상승. 반도체 수요 감소 우려.</t>
+          <t>신약 관련 기대감에도 불구하고 주가조작 의혹 및 공매도 악재로 인한 하락세 지속.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['AI', '반도체', '수요']</t>
+          <t>['주가조작', '공매도', '신약']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>106</v>
+        <v>1</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -1384,90 +1384,90 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>004310</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>흥구석유</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>14760</v>
+        <v>19010</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'+0.68%</t>
+          <t>'+1.33%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>-1.17</v>
+        <v>-0.02</v>
       </c>
       <c r="E11" t="n">
-        <v>112</v>
+        <v>45</v>
       </c>
       <c r="F11" t="n">
-        <v>75</v>
+        <v>30</v>
       </c>
       <c r="G11" t="n">
-        <v>258</v>
+        <v>166</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>10.53</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>14660</v>
+        <v>18760</v>
       </c>
       <c r="K11" t="n">
-        <v>14980</v>
+        <v>18440</v>
       </c>
       <c r="L11" t="n">
-        <v>15460</v>
+        <v>19060</v>
       </c>
       <c r="M11" t="n">
-        <v>14330</v>
+        <v>18120</v>
       </c>
       <c r="N11" t="n">
-        <v>1.17</v>
+        <v>10.55</v>
       </c>
       <c r="O11" t="n">
-        <v>32840436390</v>
+        <v>29543559870</v>
       </c>
       <c r="P11" t="n">
-        <v>36200</v>
+        <v>40350</v>
       </c>
       <c r="Q11" t="n">
-        <v>8920</v>
+        <v>3320</v>
       </c>
       <c r="R11" t="n">
-        <v>-47000</v>
+        <v>69000</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>-6000</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>이란 관련 지정학적 리스크 및 국제유가 상승으로 인한 기대감. 그러나 실제 주가 움직임은 장난질에 그치고 있으며, 유가 상승에도 불구하고 하락하는 모습.</t>
+          <t>대차해지 운동을 통한 주가 부양 기대감. AI 관련주 편입 가능성 및 해외 건설 수주.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['국제유가', '이란', '지정학적 리스크']</t>
+          <t>['대차해지', 'AI', '건설']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -1476,90 +1476,90 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>024060</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>샌즈랩</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>6940</v>
+        <v>1716000</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'+0.58%</t>
+          <t>'+1.12%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>-0.97</v>
+        <v>-0.2</v>
       </c>
       <c r="E12" t="n">
-        <v>41</v>
+        <v>800</v>
       </c>
       <c r="F12" t="n">
-        <v>25</v>
+        <v>464</v>
       </c>
       <c r="G12" t="n">
-        <v>97</v>
+        <v>2003</v>
       </c>
       <c r="H12" t="n">
-        <v>0.7</v>
+        <v>50.27</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>6900</v>
+        <v>1697000</v>
       </c>
       <c r="K12" t="n">
-        <v>7500</v>
+        <v>1690000</v>
       </c>
       <c r="L12" t="n">
-        <v>8190</v>
+        <v>1725000</v>
       </c>
       <c r="M12" t="n">
-        <v>6730</v>
+        <v>1685000</v>
       </c>
       <c r="N12" t="n">
-        <v>1.67</v>
+        <v>50.47</v>
       </c>
       <c r="O12" t="n">
-        <v>27500787800</v>
+        <v>1481639280000</v>
       </c>
       <c r="P12" t="n">
-        <v>10360</v>
+        <v>2987000</v>
       </c>
       <c r="Q12" t="n">
-        <v>2965</v>
+        <v>325000</v>
       </c>
       <c r="R12" t="n">
-        <v>35000</v>
+        <v>-66000</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>-53000</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>미국 보안주 강세와 네이버클라우드 컨소시엄 소속이라는 점을 바탕으로 594억 공급계약 및 양자암호 관련 호재 기대. 단일가 예고 공시로 인한 상승 제한 가능성.</t>
+          <t>나스닥 선물 및 코스피 야간 선물 흐름에 따른 상승 기대감. 외국인 매수세 유입 시 강한 반등 전망.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.5</v>
+        <v>0.1</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['사이버보안', '양자암호', '공급계약']</t>
+          <t>['나스닥', '외국인매수', '상승기대']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>2</v>
+        <v>71</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
@@ -1568,38 +1568,38 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>411080</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1706500</v>
+        <v>251500</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'+0.56%</t>
+          <t>'+1.00%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>-0.2</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="E13" t="n">
         <v>800</v>
       </c>
       <c r="F13" t="n">
-        <v>460</v>
+        <v>477</v>
       </c>
       <c r="G13" t="n">
-        <v>2021</v>
+        <v>2135</v>
       </c>
       <c r="H13" t="n">
-        <v>50.27</v>
+        <v>46.57</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1607,38 +1607,38 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>1697000</v>
+        <v>249000</v>
       </c>
       <c r="K13" t="n">
-        <v>1690000</v>
+        <v>248000</v>
       </c>
       <c r="L13" t="n">
-        <v>1725000</v>
+        <v>252000</v>
       </c>
       <c r="M13" t="n">
-        <v>1685000</v>
+        <v>247500</v>
       </c>
       <c r="N13" t="n">
-        <v>50.47</v>
+        <v>46.64</v>
       </c>
       <c r="O13" t="n">
-        <v>1391548537000</v>
+        <v>820840138250</v>
       </c>
       <c r="P13" t="n">
-        <v>2987000</v>
+        <v>374500</v>
       </c>
       <c r="Q13" t="n">
-        <v>325000</v>
+        <v>75900</v>
       </c>
       <c r="R13" t="n">
-        <v>-66000</v>
+        <v>-156000</v>
       </c>
       <c r="S13" t="n">
-        <v>-53000</v>
+        <v>-305000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>나스닥 선물 흐름 호조 및 조정 국면 종료 기대감. 외국인 매수 동향 주시.</t>
+          <t>반도체 수요 감소 우려 속에서도 시장 안정화 기대감 및 저가 매수 기회 모색. 정치적 이슈 관련 언급.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
@@ -1647,11 +1647,11 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['나스닥', '조정', '외국인']</t>
+          <t>['반도체', '저가매수', '시장안정']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>71</v>
+        <v>106</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
@@ -1660,38 +1660,38 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>한미반도체</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>18800</v>
+        <v>227000</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'+0.21%</t>
+          <t>'+0.89%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>-0.02</v>
+        <v>0.15</v>
       </c>
       <c r="E14" t="n">
-        <v>43</v>
+        <v>115</v>
       </c>
       <c r="F14" t="n">
-        <v>30</v>
+        <v>65</v>
       </c>
       <c r="G14" t="n">
-        <v>161</v>
+        <v>546</v>
       </c>
       <c r="H14" t="n">
-        <v>10.53</v>
+        <v>7.2</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1699,51 +1699,51 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>18760</v>
+        <v>225000</v>
       </c>
       <c r="K14" t="n">
-        <v>18440</v>
+        <v>228500</v>
       </c>
       <c r="L14" t="n">
-        <v>19060</v>
+        <v>229000</v>
       </c>
       <c r="M14" t="n">
-        <v>18120</v>
+        <v>219500</v>
       </c>
       <c r="N14" t="n">
-        <v>10.55</v>
+        <v>7.05</v>
       </c>
       <c r="O14" t="n">
-        <v>26705180425</v>
+        <v>57325801500</v>
       </c>
       <c r="P14" t="n">
-        <v>40350</v>
+        <v>426000</v>
       </c>
       <c r="Q14" t="n">
-        <v>3320</v>
+        <v>89500</v>
       </c>
       <c r="R14" t="n">
-        <v>69000</v>
+        <v>-102000</v>
       </c>
       <c r="S14" t="n">
-        <v>-6000</v>
+        <v>-2000</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>대차해지 운동을 통한 주가 부양 기대감. AI 관련주 편입 가능성 및 해외 건설 수주.</t>
+          <t>머스크 테슬라의 테라팹에 패키징 장비 공급 단독 보도 및 이에 따른 기대감 형성. 공매도 세력에 대한 언급 및 반등 기대.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.2</v>
+        <v>0.8</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['대차해지', 'AI', '건설']</t>
+          <t>['테라팹', '패키징 장비', '공매도']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
@@ -1752,86 +1752,86 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>042700</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>한미반도체</t>
+          <t>샌즈랩</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>224500</v>
+        <v>6900</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-0.22%</t>
+          <t>'+0.00%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>0.15</v>
+        <v>-0.97</v>
       </c>
       <c r="E15" t="n">
-        <v>110</v>
+        <v>39</v>
       </c>
       <c r="F15" t="n">
-        <v>62</v>
+        <v>25</v>
       </c>
       <c r="G15" t="n">
-        <v>503</v>
+        <v>93</v>
       </c>
       <c r="H15" t="n">
-        <v>7.2</v>
+        <v>0.7</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>225000</v>
+        <v>6900</v>
       </c>
       <c r="K15" t="n">
-        <v>228500</v>
+        <v>7500</v>
       </c>
       <c r="L15" t="n">
-        <v>229000</v>
+        <v>8190</v>
       </c>
       <c r="M15" t="n">
-        <v>219500</v>
+        <v>6730</v>
       </c>
       <c r="N15" t="n">
-        <v>7.05</v>
+        <v>1.67</v>
       </c>
       <c r="O15" t="n">
-        <v>54875565000</v>
+        <v>27696094990</v>
       </c>
       <c r="P15" t="n">
-        <v>426000</v>
+        <v>10360</v>
       </c>
       <c r="Q15" t="n">
-        <v>89500</v>
+        <v>2965</v>
       </c>
       <c r="R15" t="n">
-        <v>-102000</v>
+        <v>35000</v>
       </c>
       <c r="S15" t="n">
-        <v>-2000</v>
+        <v>0</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>머스크 테라팹 공급 계약 관련 단독 보도 및 나스닥 반등으로 인한 상승 기대감. 공매도 세력에 대한 언급과 함께 주주환원 정책 요구.</t>
+          <t>미국 보안주 강세와 네이버클라우드 컨소시엄 소속이라는 점을 바탕으로 594억 공급계약 및 양자암호 관련 호재 기대. 단일가 예고 공시로 인한 상승 제한 가능성.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['패키징장비', '테라팹', '공매도']</t>
+          <t>['사이버보안', '양자암호', '공급계약']</t>
         </is>
       </c>
       <c r="X15" t="n">
@@ -1839,95 +1839,95 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>042700</t>
+          <t>411080</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>LG디스플레이</t>
+          <t>흥구석유</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>8790</v>
+        <v>14630</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'-0.68%</t>
+          <t>'-0.20%</t>
         </is>
       </c>
       <c r="D16" t="n">
+        <v>-1.17</v>
+      </c>
+      <c r="E16" t="n">
+        <v>115</v>
+      </c>
+      <c r="F16" t="n">
+        <v>75</v>
+      </c>
+      <c r="G16" t="n">
+        <v>265</v>
+      </c>
+      <c r="H16" t="n">
         <v>0</v>
       </c>
-      <c r="E16" t="n">
-        <v>59</v>
-      </c>
-      <c r="F16" t="n">
-        <v>36</v>
-      </c>
-      <c r="G16" t="n">
-        <v>196</v>
-      </c>
-      <c r="H16" t="n">
-        <v>27.16</v>
-      </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>8850</v>
+        <v>14660</v>
       </c>
       <c r="K16" t="n">
-        <v>8750</v>
+        <v>14980</v>
       </c>
       <c r="L16" t="n">
-        <v>8820</v>
+        <v>15460</v>
       </c>
       <c r="M16" t="n">
-        <v>8670</v>
+        <v>14330</v>
       </c>
       <c r="N16" t="n">
-        <v>27.16</v>
+        <v>1.17</v>
       </c>
       <c r="O16" t="n">
-        <v>11638229705</v>
+        <v>34349932015</v>
       </c>
       <c r="P16" t="n">
-        <v>17950</v>
+        <v>36200</v>
       </c>
       <c r="Q16" t="n">
-        <v>8120</v>
+        <v>8920</v>
       </c>
       <c r="R16" t="n">
-        <v>-427000</v>
+        <v>-47000</v>
       </c>
       <c r="S16" t="n">
-        <v>-11000</v>
+        <v>0</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>적자 지속 및 목표주가 하향 조정 관련 부정적 언급. 경영진 사퇴 요구.</t>
+          <t>국제 유가 상승 및 지정학적 리스크(이란, 후티 반군) 관련 언급과 함께 유가 하락 및 장난질에 대한 부정적 전망 혼재.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['적자', '목표주가', '경영진']</t>
+          <t>['국제유가', '지정학적 리스크', '헤지주']</t>
         </is>
       </c>
       <c r="X16" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
@@ -1936,77 +1936,77 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>034220</t>
+          <t>024060</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>LG디스플레이</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>14240</v>
+        <v>8810</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'-1.73%</t>
+          <t>'-0.45%</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>-0.08</v>
+        <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="F17" t="n">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="G17" t="n">
-        <v>272</v>
+        <v>204</v>
       </c>
       <c r="H17" t="n">
-        <v>1.8</v>
+        <v>27.16</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>14490</v>
+        <v>8850</v>
       </c>
       <c r="K17" t="n">
-        <v>14410</v>
+        <v>8750</v>
       </c>
       <c r="L17" t="n">
-        <v>14600</v>
+        <v>8820</v>
       </c>
       <c r="M17" t="n">
-        <v>13930</v>
+        <v>8670</v>
       </c>
       <c r="N17" t="n">
-        <v>1.88</v>
+        <v>27.16</v>
       </c>
       <c r="O17" t="n">
-        <v>33956077550</v>
+        <v>12414872385</v>
       </c>
       <c r="P17" t="n">
-        <v>31500</v>
+        <v>17950</v>
       </c>
       <c r="Q17" t="n">
-        <v>1272</v>
+        <v>8120</v>
       </c>
       <c r="R17" t="n">
-        <v>6000</v>
+        <v>-427000</v>
       </c>
       <c r="S17" t="n">
-        <v>-9000</v>
+        <v>-11000</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>머니투데이 방송 홍보 언급 있으나, 미증시 하락 및 FOMC 금리, 유가 등 변수로 인한 하락세. 외국인 보유율이 낮다는 점은 긍정적 요인.</t>
+          <t>키움증권의 목표주가 하향 조정 및 PBR 저평가 논란. 삼성디스플레이와의 비교를 통한 부정적 전망.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
@@ -2015,11 +2015,11 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['광통신', 'FOMC', '유가']</t>
+          <t>['목표주가', 'PBR', '키움증권']</t>
         </is>
       </c>
       <c r="X17" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
@@ -2028,7 +2028,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>034220</t>
         </is>
       </c>
     </row>
@@ -2039,24 +2039,24 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>85450</v>
+        <v>86500</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'-1.78%</t>
+          <t>'-0.57%</t>
         </is>
       </c>
       <c r="D18" t="n">
         <v>-0.11</v>
       </c>
       <c r="E18" t="n">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="F18" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G18" t="n">
-        <v>511</v>
+        <v>560</v>
       </c>
       <c r="H18" t="n">
         <v>23.45</v>
@@ -2073,7 +2073,7 @@
         <v>86200</v>
       </c>
       <c r="L18" t="n">
-        <v>86500</v>
+        <v>86600</v>
       </c>
       <c r="M18" t="n">
         <v>85000</v>
@@ -2082,7 +2082,7 @@
         <v>23.56</v>
       </c>
       <c r="O18" t="n">
-        <v>53849699900</v>
+        <v>59732801750</v>
       </c>
       <c r="P18" t="n">
         <v>139200</v>
@@ -2098,16 +2098,16 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>미국 엑스에너지 급등 및 원전 관련 ETF 출시 소식으로 인한 상승 기대감. 중앙아시아 5개국 협력 가능성 언급.</t>
+          <t>원전 사업 강화 및 ETF 추가 출시 관련 긍정적 전망. 엑스에너지 급등, 웨스팅하우스 등 관련 이슈 언급. 일부 하락 후 반등 기대.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['원전', '엑스에너지', 'ETF']</t>
+          <t>['원전', 'ETF', '엑스에너지']</t>
         </is>
       </c>
       <c r="X18" t="n">
@@ -2127,83 +2127,83 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>삼성중공업</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>21300</v>
+        <v>14300</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'-3.62%</t>
+          <t>'-1.31%</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>0.09</v>
+        <v>-0.08</v>
       </c>
       <c r="E19" t="n">
-        <v>83</v>
+        <v>70</v>
       </c>
       <c r="F19" t="n">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="G19" t="n">
-        <v>190</v>
+        <v>282</v>
       </c>
       <c r="H19" t="n">
-        <v>28.9</v>
+        <v>1.8</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>22100</v>
+        <v>14490</v>
       </c>
       <c r="K19" t="n">
-        <v>21850</v>
+        <v>14410</v>
       </c>
       <c r="L19" t="n">
-        <v>21850</v>
+        <v>14600</v>
       </c>
       <c r="M19" t="n">
-        <v>21150</v>
+        <v>13930</v>
       </c>
       <c r="N19" t="n">
-        <v>28.81</v>
+        <v>1.88</v>
       </c>
       <c r="O19" t="n">
-        <v>26880808900</v>
+        <v>35620215380</v>
       </c>
       <c r="P19" t="n">
-        <v>35350</v>
+        <v>31500</v>
       </c>
       <c r="Q19" t="n">
-        <v>18440</v>
+        <v>1272</v>
       </c>
       <c r="R19" t="n">
-        <v>-616000</v>
+        <v>6000</v>
       </c>
       <c r="S19" t="n">
-        <v>-49000</v>
+        <v>-9000</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>12억 달러 규모 수주 공시 확인. 금투, 투신, 연기금 등 기관 매도세 및 주포 악질 행태 경고.</t>
+          <t>머니투데이 방송 홍보 언급 있으나, 미증시 하락 및 FOMC 금리, 유가 등 변수로 인한 하락세. 외국인 보유율이 낮다는 점은 긍정적 요인.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
       <c r="V19" t="n">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['수주', '기관', '주포']</t>
+          <t>['광통신', 'FOMC', '유가']</t>
         </is>
       </c>
       <c r="X19" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
@@ -2212,7 +2212,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>010140</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
@@ -2223,24 +2223,24 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>4162</v>
+        <v>4175</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>'-3.77%</t>
+          <t>'-3.47%</t>
         </is>
       </c>
       <c r="D20" t="n">
         <v>0.18</v>
       </c>
       <c r="E20" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F20" t="n">
         <v>31</v>
       </c>
       <c r="G20" t="n">
-        <v>119</v>
+        <v>132</v>
       </c>
       <c r="H20" t="n">
         <v>0.77</v>
@@ -2266,7 +2266,7 @@
         <v>0.59</v>
       </c>
       <c r="O20" t="n">
-        <v>40214815813</v>
+        <v>41463832568</v>
       </c>
       <c r="P20" t="n">
         <v>8100</v>
@@ -2282,7 +2282,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>미국 기업과 594억 공급 계약 호재. 광통신 및 5G 관련주와 비교되며 주가 상승 기대. 광전자 대비 낮은 상승률.</t>
+          <t>미국 기업과의 공급 계약 관련 긍정적 언급과 폭락 및 속지 말라는 부정적 의견 혼재. 광통신 및 5G 테마 부진 언급.</t>
         </is>
       </c>
       <c r="U20" t="inlineStr"/>
@@ -2291,7 +2291,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>['공급 계약', '광통신', '5G']</t>
+          <t>['공급 계약', '폭락', '광통신']</t>
         </is>
       </c>
       <c r="X20" t="n">
@@ -2305,6 +2305,98 @@
       <c r="Z20" t="inlineStr">
         <is>
           <t>069540</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>삼성중공업</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>21300</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>'-3.62%</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="E21" t="n">
+        <v>85</v>
+      </c>
+      <c r="F21" t="n">
+        <v>54</v>
+      </c>
+      <c r="G21" t="n">
+        <v>212</v>
+      </c>
+      <c r="H21" t="n">
+        <v>28.9</v>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J21" t="n">
+        <v>22100</v>
+      </c>
+      <c r="K21" t="n">
+        <v>21850</v>
+      </c>
+      <c r="L21" t="n">
+        <v>21850</v>
+      </c>
+      <c r="M21" t="n">
+        <v>21150</v>
+      </c>
+      <c r="N21" t="n">
+        <v>28.81</v>
+      </c>
+      <c r="O21" t="n">
+        <v>29583957600</v>
+      </c>
+      <c r="P21" t="n">
+        <v>35350</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>18440</v>
+      </c>
+      <c r="R21" t="n">
+        <v>-616000</v>
+      </c>
+      <c r="S21" t="n">
+        <v>-49000</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>12억 달러 규모 수주 공시에도 불구하고 외국인, 기관 매도세와 함께 주가 하락. 악질 주포 및 신뢰도 낮은 기업으로 평가.</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr"/>
+      <c r="V21" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>['수주공시', '기관매도', '주포']</t>
+        </is>
+      </c>
+      <c r="X21" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>010140</t>
         </is>
       </c>
     </row>

--- a/data/trending_integrated_20260915_10.xlsx
+++ b/data/trending_integrated_20260915_10.xlsx
@@ -567,18 +567,18 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>10920</v>
+        <v>10910</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+17.80%</t>
+          <t>'+17.69%</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>-0.06</v>
       </c>
       <c r="E2" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F2" t="n">
         <v>46</v>
@@ -610,7 +610,7 @@
         <v>1.25</v>
       </c>
       <c r="O2" t="n">
-        <v>112502958960</v>
+        <v>115031128035</v>
       </c>
       <c r="P2" t="n">
         <v>25050</v>
@@ -626,16 +626,16 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>세계 최초 면역조절 펩타이드 장기지속형 제제 기술 특허 등록 및 품절주 관련 언급. 다만, 급등락 및 일부 부정적 의견 혼재.</t>
+          <t>면역조절 펩타이드 장기지속형 제제 기술 특허 등록 소식에 품절주로 언급되며 목표가 상향 기대감.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['품절주', '특허 등록', '장기지속형']</t>
+          <t>['면역조절', '펩타이드', '품절주']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2915</v>
+        <v>2880</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+12.77%</t>
+          <t>'+11.41%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>1.34</v>
       </c>
       <c r="E3" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="F3" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G3" t="n">
-        <v>110</v>
+        <v>122</v>
       </c>
       <c r="H3" t="n">
         <v>1.34</v>
@@ -702,7 +702,7 @@
         <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>58743564785</v>
+        <v>60010983744</v>
       </c>
       <c r="P3" t="n">
         <v>5100</v>
@@ -718,7 +718,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>미국 기업과의 594억 규모 공급 계약 체결 및 세계 최초 타이틀 관련 호재. AI 발전 수혜 기대감.</t>
+          <t>594억 공급 계약 및 AI 관련 호재로 급등. 거래량 동반하며 신고가 경신 기대감 고조.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
@@ -727,7 +727,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['공급계약', 'AI', '세계최초']</t>
+          <t>['공급 계약', 'AI', '급등']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -747,83 +747,83 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>현대제철</t>
+          <t>JW신약</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>36000</v>
+        <v>3690</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+9.09%</t>
+          <t>'+8.53%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>-0.13</v>
+        <v>0.12</v>
       </c>
       <c r="E4" t="n">
-        <v>41</v>
+        <v>62</v>
       </c>
       <c r="F4" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G4" t="n">
-        <v>161</v>
+        <v>153</v>
       </c>
       <c r="H4" t="n">
-        <v>14.93</v>
+        <v>0.83</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>33000</v>
+        <v>3400</v>
       </c>
       <c r="K4" t="n">
-        <v>32750</v>
+        <v>3450</v>
       </c>
       <c r="L4" t="n">
-        <v>37200</v>
+        <v>4080</v>
       </c>
       <c r="M4" t="n">
-        <v>32750</v>
+        <v>3445</v>
       </c>
       <c r="N4" t="n">
-        <v>15.06</v>
+        <v>0.71</v>
       </c>
       <c r="O4" t="n">
-        <v>32114228200</v>
+        <v>131093277303</v>
       </c>
       <c r="P4" t="n">
-        <v>50400</v>
+        <v>4335</v>
       </c>
       <c r="Q4" t="n">
-        <v>23650</v>
+        <v>1246</v>
       </c>
       <c r="R4" t="n">
-        <v>126000</v>
+        <v>59000</v>
       </c>
       <c r="S4" t="n">
-        <v>5000</v>
+        <v>0</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>초장기 상승 추세 및 저 PBR 이슈에 따른 120일선 돌파. 한국거래소의 저평가 기업 정책 기대감.</t>
+          <t>프로그램 매도 후 외국인 순매수 전환 및 4천원 안착 시도. 삼익제약과의 비교를 통한 대장주 경쟁.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['저PBR', '120일선', '정배열']</t>
+          <t>['외국인순매수', '프로그램', '단타']</t>
         </is>
       </c>
       <c r="X4" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
@@ -832,90 +832,90 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>004020</t>
+          <t>067290</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>JW신약</t>
+          <t>현대제철</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3695</v>
+        <v>36000</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+8.68%</t>
+          <t>'+7.14%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.12</v>
+        <v>-0.13</v>
       </c>
       <c r="E5" t="n">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="F5" t="n">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="G5" t="n">
-        <v>150</v>
+        <v>174</v>
       </c>
       <c r="H5" t="n">
-        <v>0.83</v>
+        <v>14.93</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>3400</v>
+        <v>33600</v>
       </c>
       <c r="K5" t="n">
-        <v>3450</v>
+        <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>4080</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>3445</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>0.71</v>
+        <v>15.06</v>
       </c>
       <c r="O5" t="n">
-        <v>129630417308</v>
+        <v>34765000000</v>
       </c>
       <c r="P5" t="n">
-        <v>4335</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>1246</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>59000</v>
+        <v>126000</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>프로그램 매도 후 외국인 순매수 전환 및 4천원 안착 시도. 삼익제약과의 비교를 통한 대장주 경쟁.</t>
+          <t>저 PBR 기업으로 분류되어 상승 기대감 높음. 120일선 돌파 및 정배열 초기 국면 진입 분석.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.1</v>
+        <v>0.6</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['외국인순매수', '프로그램', '단타']</t>
+          <t>['저PBR', '120일선', '정배열']</t>
         </is>
       </c>
       <c r="X5" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
@@ -924,7 +924,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>067290</t>
+          <t>004020</t>
         </is>
       </c>
     </row>
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>14980</v>
+        <v>14750</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+6.17%</t>
+          <t>'+4.54%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>0.06</v>
       </c>
       <c r="E6" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F6" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G6" t="n">
-        <v>103</v>
+        <v>116</v>
       </c>
       <c r="H6" t="n">
         <v>10.75</v>
@@ -978,7 +978,7 @@
         <v>10.69</v>
       </c>
       <c r="O6" t="n">
-        <v>81110940195</v>
+        <v>84366321390</v>
       </c>
       <c r="P6" t="n">
         <v>23550</v>
@@ -994,16 +994,16 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>주요 저항선인 15000원 돌파 시도 및 거래량 증가. 주포의 의도에 따른 상승 기대감과 오전 매도 물량 출회.</t>
+          <t>15000원 돌파에 대한 기대감 속 공매도 세력 관련 언급. 거래량 증가 및 주가 변동성 나타남.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.1</v>
+        <v>0.4</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['주포', '거래량', '저항선']</t>
+          <t>['공매도', '거래량', '주가 변동성']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1027,24 +1027,24 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>142100</v>
+        <v>142200</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+3.95%</t>
+          <t>'+4.02%</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>0.05</v>
       </c>
       <c r="E7" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F7" t="n">
         <v>57</v>
       </c>
       <c r="G7" t="n">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="H7" t="n">
         <v>15.81</v>
@@ -1070,7 +1070,7 @@
         <v>15.76</v>
       </c>
       <c r="O7" t="n">
-        <v>73020688250</v>
+        <v>75086924850</v>
       </c>
       <c r="P7" t="n">
         <v>164700</v>
@@ -1086,16 +1086,16 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>합병 철회 가능성 및 정규장 시작 시 주가 하락 우려. 영업이익 10조 언급과 관련한 불확실성.</t>
+          <t>정유 및 배터리 업황 호조에도 불구하고, 합병 관련 불확실성 및 기관/외인 매도세로 인한 하락.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['합병', '영업이익', '주가 하락']</t>
+          <t>['정유', '배터리', '합병']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1119,24 +1119,24 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>10650</v>
+        <v>10630</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+3.70%</t>
+          <t>'+3.51%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>0.26</v>
       </c>
       <c r="E8" t="n">
-        <v>101</v>
+        <v>108</v>
       </c>
       <c r="F8" t="n">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="G8" t="n">
-        <v>274</v>
+        <v>286</v>
       </c>
       <c r="H8" t="n">
         <v>17.93</v>
@@ -1162,7 +1162,7 @@
         <v>17.67</v>
       </c>
       <c r="O8" t="n">
-        <v>237979448325</v>
+        <v>249171152935</v>
       </c>
       <c r="P8" t="n">
         <v>22450</v>
@@ -1178,12 +1178,12 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>광통신 대장주 한국첨단소재의 급등과 트럼프 AI 정책 관련 기대감. 미국 반도체 지수 하락에도 아이온큐의 양전 마감 및 기타 법인의 매수세 유입.</t>
+          <t>트럼프 AI 정책 기대감 속 광통신 테마 상승. 아이온큐 프리마켓 급등 및 외인 매수세 유입.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
@@ -1211,24 +1211,24 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>31300</v>
+        <v>31400</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+3.13%</t>
+          <t>'+3.46%</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>-0.05</v>
       </c>
       <c r="E9" t="n">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="F9" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="G9" t="n">
-        <v>480</v>
+        <v>491</v>
       </c>
       <c r="H9" t="n">
         <v>17.5</v>
@@ -1254,7 +1254,7 @@
         <v>17.55</v>
       </c>
       <c r="O9" t="n">
-        <v>5183884375</v>
+        <v>5818211575</v>
       </c>
       <c r="P9" t="n">
         <v>69200</v>
@@ -1270,16 +1270,16 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>HLB 리보세라닙 간암 및 담관암 FDA 승인 관련 기대감과 함께, 제약 유증 및 CRL 공시로 인한 부정적 전망. 기관 및 외인 이탈 관측.</t>
+          <t>담관암 신약 FDA 승인 기대감 속 유증 이슈 및 기관/외인 매도세로 인한 하락.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['리보세라닙', 'FDA', '담관암']</t>
+          <t>['담관암', 'FDA승인', '유증']</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1299,31 +1299,31 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>현대약품</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>10130</v>
+        <v>1717000</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+1.40%</t>
+          <t>'+1.18%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>-0.2</v>
       </c>
       <c r="E10" t="n">
-        <v>59</v>
+        <v>800</v>
       </c>
       <c r="F10" t="n">
-        <v>33</v>
+        <v>458</v>
       </c>
       <c r="G10" t="n">
-        <v>72</v>
+        <v>1988</v>
       </c>
       <c r="H10" t="n">
-        <v>0.6</v>
+        <v>50.27</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1331,51 +1331,51 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>9990</v>
+        <v>1697000</v>
       </c>
       <c r="K10" t="n">
-        <v>10110</v>
+        <v>1690000</v>
       </c>
       <c r="L10" t="n">
-        <v>11390</v>
+        <v>1725000</v>
       </c>
       <c r="M10" t="n">
-        <v>10040</v>
+        <v>1685000</v>
       </c>
       <c r="N10" t="n">
-        <v>0.6</v>
+        <v>50.47</v>
       </c>
       <c r="O10" t="n">
-        <v>137462128065</v>
+        <v>1591187822500</v>
       </c>
       <c r="P10" t="n">
-        <v>15960</v>
+        <v>2987000</v>
       </c>
       <c r="Q10" t="n">
-        <v>3500</v>
+        <v>325000</v>
       </c>
       <c r="R10" t="n">
-        <v>220000</v>
+        <v>-66000</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>-53000</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>신약 관련 기대감에도 불구하고 주가조작 의혹 및 공매도 악재로 인한 하락세 지속.</t>
+          <t>조정 마무리 및 상승 전환 기대감. 나스닥 선물 흐름 및 외인 매수세 유입 시 추가 상승 전망.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['주가조작', '공매도', '신약']</t>
+          <t>['조정', '나스닥 선물', '외인 매수']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>1</v>
+        <v>71</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -1384,38 +1384,38 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>004310</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>현대약품</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>19010</v>
+        <v>10100</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'+1.33%</t>
+          <t>'+1.10%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>-0.02</v>
+        <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="F11" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G11" t="n">
-        <v>166</v>
+        <v>72</v>
       </c>
       <c r="H11" t="n">
-        <v>10.53</v>
+        <v>0.6</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1423,38 +1423,38 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>18760</v>
+        <v>9990</v>
       </c>
       <c r="K11" t="n">
-        <v>18440</v>
+        <v>10110</v>
       </c>
       <c r="L11" t="n">
-        <v>19060</v>
+        <v>11390</v>
       </c>
       <c r="M11" t="n">
-        <v>18120</v>
+        <v>10040</v>
       </c>
       <c r="N11" t="n">
-        <v>10.55</v>
+        <v>0.6</v>
       </c>
       <c r="O11" t="n">
-        <v>29543559870</v>
+        <v>138885087000</v>
       </c>
       <c r="P11" t="n">
-        <v>40350</v>
+        <v>15960</v>
       </c>
       <c r="Q11" t="n">
-        <v>3320</v>
+        <v>3500</v>
       </c>
       <c r="R11" t="n">
-        <v>69000</v>
+        <v>220000</v>
       </c>
       <c r="S11" t="n">
-        <v>-6000</v>
+        <v>0</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>대차해지 운동을 통한 주가 부양 기대감. AI 관련주 편입 가능성 및 해외 건설 수주.</t>
+          <t>주가 조작 의혹 및 공매도 관련 부정적 언급 다수. 신약 관련 기대감은 있으나 주가에 미반영.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
@@ -1463,11 +1463,11 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['대차해지', 'AI', '건설']</t>
+          <t>['주가 조작', '공매도', '신약']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -1476,90 +1476,90 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>004310</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>샌즈랩</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1716000</v>
+        <v>6950</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'+1.12%</t>
+          <t>'+0.72%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>-0.2</v>
+        <v>-0.97</v>
       </c>
       <c r="E12" t="n">
-        <v>800</v>
+        <v>40</v>
       </c>
       <c r="F12" t="n">
-        <v>464</v>
+        <v>26</v>
       </c>
       <c r="G12" t="n">
-        <v>2003</v>
+        <v>94</v>
       </c>
       <c r="H12" t="n">
-        <v>50.27</v>
+        <v>0.7</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>1697000</v>
+        <v>6900</v>
       </c>
       <c r="K12" t="n">
-        <v>1690000</v>
+        <v>7500</v>
       </c>
       <c r="L12" t="n">
-        <v>1725000</v>
+        <v>8190</v>
       </c>
       <c r="M12" t="n">
-        <v>1685000</v>
+        <v>6730</v>
       </c>
       <c r="N12" t="n">
-        <v>50.47</v>
+        <v>1.67</v>
       </c>
       <c r="O12" t="n">
-        <v>1481639280000</v>
+        <v>27803651910</v>
       </c>
       <c r="P12" t="n">
-        <v>2987000</v>
+        <v>10360</v>
       </c>
       <c r="Q12" t="n">
-        <v>325000</v>
+        <v>2965</v>
       </c>
       <c r="R12" t="n">
-        <v>-66000</v>
+        <v>35000</v>
       </c>
       <c r="S12" t="n">
-        <v>-53000</v>
+        <v>0</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>나스닥 선물 및 코스피 야간 선물 흐름에 따른 상승 기대감. 외국인 매수세 유입 시 강한 반등 전망.</t>
+          <t>미국 보안주 강세와 함께 사이버 보안 테마로 엮이며, 미국 기업과 594억 공급계약 및 양자암호 관련 기대감.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.1</v>
+        <v>0.5</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['나스닥', '외국인매수', '상승기대']</t>
+          <t>['사이버보안', '양자암호', '공급계약']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>71</v>
+        <v>2</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
@@ -1568,7 +1568,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>411080</t>
         </is>
       </c>
     </row>
@@ -1579,11 +1579,11 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>251500</v>
+        <v>250750</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'+1.00%</t>
+          <t>'+0.70%</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -1593,10 +1593,10 @@
         <v>800</v>
       </c>
       <c r="F13" t="n">
-        <v>477</v>
+        <v>470</v>
       </c>
       <c r="G13" t="n">
-        <v>2135</v>
+        <v>2014</v>
       </c>
       <c r="H13" t="n">
         <v>46.57</v>
@@ -1622,7 +1622,7 @@
         <v>46.64</v>
       </c>
       <c r="O13" t="n">
-        <v>820840138250</v>
+        <v>881534155500</v>
       </c>
       <c r="P13" t="n">
         <v>374500</v>
@@ -1638,16 +1638,16 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>반도체 수요 감소 우려 속에서도 시장 안정화 기대감 및 저가 매수 기회 모색. 정치적 이슈 관련 언급.</t>
+          <t>AI 관련 기대감과 시장 안정에 대한 낙관론 존재. 그러나 정치적 이슈 및 반도체 시장 불안감으로 하락 전망도 공존.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['반도체', '저가매수', '시장안정']</t>
+          <t>['AI', '반도체', '시장 전망']</t>
         </is>
       </c>
       <c r="X13" t="n">
@@ -1667,31 +1667,31 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>한미반도체</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>227000</v>
+        <v>18890</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'+0.89%</t>
+          <t>'+0.69%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0.15</v>
+        <v>-0.02</v>
       </c>
       <c r="E14" t="n">
-        <v>115</v>
+        <v>46</v>
       </c>
       <c r="F14" t="n">
-        <v>65</v>
+        <v>31</v>
       </c>
       <c r="G14" t="n">
-        <v>546</v>
+        <v>190</v>
       </c>
       <c r="H14" t="n">
-        <v>7.2</v>
+        <v>10.53</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1699,51 +1699,51 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>225000</v>
+        <v>18760</v>
       </c>
       <c r="K14" t="n">
-        <v>228500</v>
+        <v>18440</v>
       </c>
       <c r="L14" t="n">
-        <v>229000</v>
+        <v>19060</v>
       </c>
       <c r="M14" t="n">
-        <v>219500</v>
+        <v>18120</v>
       </c>
       <c r="N14" t="n">
-        <v>7.05</v>
+        <v>10.55</v>
       </c>
       <c r="O14" t="n">
-        <v>57325801500</v>
+        <v>32106219130</v>
       </c>
       <c r="P14" t="n">
-        <v>426000</v>
+        <v>40350</v>
       </c>
       <c r="Q14" t="n">
-        <v>89500</v>
+        <v>3320</v>
       </c>
       <c r="R14" t="n">
-        <v>-102000</v>
+        <v>69000</v>
       </c>
       <c r="S14" t="n">
-        <v>-2000</v>
+        <v>-6000</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>머스크 테슬라의 테라팹에 패키징 장비 공급 단독 보도 및 이에 따른 기대감 형성. 공매도 세력에 대한 언급 및 반등 기대.</t>
+          <t>대차해지 운동 참여 독려 및 건설 대장주로서의 기대감 표출. 해외 건설 수주 가능성 언급.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.8</v>
+        <v>0.3</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['테라팹', '패키징 장비', '공매도']</t>
+          <t>['대차해지', '해외건설', '건설 대장주']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
@@ -1752,38 +1752,38 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>042700</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>샌즈랩</t>
+          <t>흥구석유</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>6900</v>
+        <v>14760</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'+0.00%</t>
+          <t>'+0.68%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>-0.97</v>
+        <v>-1.17</v>
       </c>
       <c r="E15" t="n">
-        <v>39</v>
+        <v>122</v>
       </c>
       <c r="F15" t="n">
-        <v>25</v>
+        <v>78</v>
       </c>
       <c r="G15" t="n">
-        <v>93</v>
+        <v>278</v>
       </c>
       <c r="H15" t="n">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1791,143 +1791,143 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>6900</v>
+        <v>14660</v>
       </c>
       <c r="K15" t="n">
-        <v>7500</v>
+        <v>14980</v>
       </c>
       <c r="L15" t="n">
-        <v>8190</v>
+        <v>15460</v>
       </c>
       <c r="M15" t="n">
-        <v>6730</v>
+        <v>14330</v>
       </c>
       <c r="N15" t="n">
-        <v>1.67</v>
+        <v>1.17</v>
       </c>
       <c r="O15" t="n">
-        <v>27696094990</v>
+        <v>35090998705</v>
       </c>
       <c r="P15" t="n">
-        <v>10360</v>
+        <v>36200</v>
       </c>
       <c r="Q15" t="n">
-        <v>2965</v>
+        <v>8920</v>
       </c>
       <c r="R15" t="n">
-        <v>35000</v>
+        <v>-47000</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>미국 보안주 강세와 네이버클라우드 컨소시엄 소속이라는 점을 바탕으로 594억 공급계약 및 양자암호 관련 호재 기대. 단일가 예고 공시로 인한 상승 제한 가능성.</t>
+          <t>국제 유가 상승 및 지정학적 리스크(이란, 후티 반군) 관련 언급과 함께 유가 하락 및 장난질에 대한 부정적 전망 혼재.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['사이버보안', '양자암호', '공급계약']</t>
+          <t>['국제유가', '지정학적 리스크', '헤지주']</t>
         </is>
       </c>
       <c r="X15" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>411080</t>
+          <t>024060</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>흥구석유</t>
+          <t>한미반도체</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>14630</v>
+        <v>225500</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'-0.20%</t>
+          <t>'+0.22%</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>-1.17</v>
+        <v>0.15</v>
       </c>
       <c r="E16" t="n">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="F16" t="n">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="G16" t="n">
-        <v>265</v>
+        <v>566</v>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>14660</v>
+        <v>225000</v>
       </c>
       <c r="K16" t="n">
-        <v>14980</v>
+        <v>228500</v>
       </c>
       <c r="L16" t="n">
-        <v>15460</v>
+        <v>229000</v>
       </c>
       <c r="M16" t="n">
-        <v>14330</v>
+        <v>219500</v>
       </c>
       <c r="N16" t="n">
-        <v>1.17</v>
+        <v>7.05</v>
       </c>
       <c r="O16" t="n">
-        <v>34349932015</v>
+        <v>59186575000</v>
       </c>
       <c r="P16" t="n">
-        <v>36200</v>
+        <v>426000</v>
       </c>
       <c r="Q16" t="n">
-        <v>8920</v>
+        <v>89500</v>
       </c>
       <c r="R16" t="n">
-        <v>-47000</v>
+        <v>-102000</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>-2000</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>국제 유가 상승 및 지정학적 리스크(이란, 후티 반군) 관련 언급과 함께 유가 하락 및 장난질에 대한 부정적 전망 혼재.</t>
+          <t>머스크 테슬라의 테라팹에 패키징 장비 공급 단독 보도 및 이에 따른 기대감 형성. 공매도 세력에 대한 언급 및 반등 기대.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['국제유가', '지정학적 리스크', '헤지주']</t>
+          <t>['테라팹', '패키징 장비', '공매도']</t>
         </is>
       </c>
       <c r="X16" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
@@ -1936,7 +1936,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>024060</t>
+          <t>042700</t>
         </is>
       </c>
     </row>
@@ -1947,24 +1947,24 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>8810</v>
+        <v>8800</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'-0.45%</t>
+          <t>'-0.56%</t>
         </is>
       </c>
       <c r="D17" t="n">
         <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="F17" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G17" t="n">
-        <v>204</v>
+        <v>212</v>
       </c>
       <c r="H17" t="n">
         <v>27.16</v>
@@ -1981,7 +1981,7 @@
         <v>8750</v>
       </c>
       <c r="L17" t="n">
-        <v>8820</v>
+        <v>8840</v>
       </c>
       <c r="M17" t="n">
         <v>8670</v>
@@ -1990,7 +1990,7 @@
         <v>27.16</v>
       </c>
       <c r="O17" t="n">
-        <v>12414872385</v>
+        <v>12912772655</v>
       </c>
       <c r="P17" t="n">
         <v>17950</v>
@@ -2006,16 +2006,16 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>키움증권의 목표주가 하향 조정 및 PBR 저평가 논란. 삼성디스플레이와의 비교를 통한 부정적 전망.</t>
+          <t>목표 주가 하향 조정 및 연속 적자에 대한 비판. 삼성디스플레이와 비교하며 저평가 주장도 있으나 부정적 전망 우세.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['목표주가', 'PBR', '키움증권']</t>
+          <t>['목표주가', '적자', '저평가']</t>
         </is>
       </c>
       <c r="X17" t="n">
@@ -2039,24 +2039,24 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>86500</v>
+        <v>85800</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'-0.57%</t>
+          <t>'-1.38%</t>
         </is>
       </c>
       <c r="D18" t="n">
         <v>-0.11</v>
       </c>
       <c r="E18" t="n">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="F18" t="n">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="G18" t="n">
-        <v>560</v>
+        <v>585</v>
       </c>
       <c r="H18" t="n">
         <v>23.45</v>
@@ -2073,7 +2073,7 @@
         <v>86200</v>
       </c>
       <c r="L18" t="n">
-        <v>86600</v>
+        <v>86700</v>
       </c>
       <c r="M18" t="n">
         <v>85000</v>
@@ -2082,7 +2082,7 @@
         <v>23.56</v>
       </c>
       <c r="O18" t="n">
-        <v>59732801750</v>
+        <v>64340610700</v>
       </c>
       <c r="P18" t="n">
         <v>139200</v>
@@ -2098,16 +2098,16 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>원전 사업 강화 및 ETF 추가 출시 관련 긍정적 전망. 엑스에너지 급등, 웨스팅하우스 등 관련 이슈 언급. 일부 하락 후 반등 기대.</t>
+          <t>원전 관련 ETF 출시 및 X에너지 급등에 따른 기대감 속에서, 전날 하락에 대한 반발 매수세 유입.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['원전', 'ETF', '엑스에너지']</t>
+          <t>['원전', 'ETF', '에너지']</t>
         </is>
       </c>
       <c r="X18" t="n">
@@ -2131,24 +2131,24 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>14300</v>
+        <v>14250</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'-1.31%</t>
+          <t>'-1.66%</t>
         </is>
       </c>
       <c r="D19" t="n">
         <v>-0.08</v>
       </c>
       <c r="E19" t="n">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="F19" t="n">
         <v>45</v>
       </c>
       <c r="G19" t="n">
-        <v>282</v>
+        <v>303</v>
       </c>
       <c r="H19" t="n">
         <v>1.8</v>
@@ -2174,7 +2174,7 @@
         <v>1.88</v>
       </c>
       <c r="O19" t="n">
-        <v>35620215380</v>
+        <v>38650002930</v>
       </c>
       <c r="P19" t="n">
         <v>31500</v>
@@ -2190,16 +2190,16 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>머니투데이 방송 홍보 언급 있으나, 미증시 하락 및 FOMC 금리, 유가 등 변수로 인한 하락세. 외국인 보유율이 낮다는 점은 긍정적 요인.</t>
+          <t>머니투데이 방송 홍보에도 불구하고 미증시 하락 및 AI, FOMC 등 거시경제 변수로 인한 보합세.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
       <c r="V19" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['광통신', 'FOMC', '유가']</t>
+          <t>['광통신', '외국인매수', 'AI']</t>
         </is>
       </c>
       <c r="X19" t="n">
@@ -2223,24 +2223,24 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>4175</v>
+        <v>4185</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>'-3.47%</t>
+          <t>'-3.24%</t>
         </is>
       </c>
       <c r="D20" t="n">
         <v>0.18</v>
       </c>
       <c r="E20" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="F20" t="n">
         <v>31</v>
       </c>
       <c r="G20" t="n">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="H20" t="n">
         <v>0.77</v>
@@ -2266,7 +2266,7 @@
         <v>0.59</v>
       </c>
       <c r="O20" t="n">
-        <v>41463832568</v>
+        <v>43758966217</v>
       </c>
       <c r="P20" t="n">
         <v>8100</v>
@@ -2282,7 +2282,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>미국 기업과의 공급 계약 관련 긍정적 언급과 폭락 및 속지 말라는 부정적 의견 혼재. 광통신 및 5G 테마 부진 언급.</t>
+          <t>삼성SDS와 4381억 공급계약 공시에도 불구하고 광통신 및 5G 테마 부진으로 인한 하락세.</t>
         </is>
       </c>
       <c r="U20" t="inlineStr"/>
@@ -2291,7 +2291,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>['공급 계약', '폭락', '광통신']</t>
+          <t>['공급계약', '광통신', '5G']</t>
         </is>
       </c>
       <c r="X20" t="n">
@@ -2315,24 +2315,24 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>21300</v>
+        <v>21175</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>'-3.62%</t>
+          <t>'-4.19%</t>
         </is>
       </c>
       <c r="D21" t="n">
         <v>0.09</v>
       </c>
       <c r="E21" t="n">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="F21" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="G21" t="n">
-        <v>212</v>
+        <v>227</v>
       </c>
       <c r="H21" t="n">
         <v>28.9</v>
@@ -2358,7 +2358,7 @@
         <v>28.81</v>
       </c>
       <c r="O21" t="n">
-        <v>29583957600</v>
+        <v>32312969075</v>
       </c>
       <c r="P21" t="n">
         <v>35350</v>
@@ -2374,16 +2374,16 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>12억 달러 규모 수주 공시에도 불구하고 외국인, 기관 매도세와 함께 주가 하락. 악질 주포 및 신뢰도 낮은 기업으로 평가.</t>
+          <t>12억 달러 수주 공시에도 불구하고 주가 하락에 대한 불만 다수. 악성 루머 및 신뢰도 저하 언급.</t>
         </is>
       </c>
       <c r="U21" t="inlineStr"/>
       <c r="V21" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>['수주공시', '기관매도', '주포']</t>
+          <t>['수주 공시', '주가 하락', '신뢰도']</t>
         </is>
       </c>
       <c r="X21" t="n">

--- a/data/trending_integrated_20260915_10.xlsx
+++ b/data/trending_integrated_20260915_10.xlsx
@@ -567,24 +567,24 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>10910</v>
+        <v>10970</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+17.69%</t>
+          <t>'+18.34%</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>-0.06</v>
       </c>
       <c r="E2" t="n">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="F2" t="n">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="G2" t="n">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="H2" t="n">
         <v>1.19</v>
@@ -610,7 +610,7 @@
         <v>1.25</v>
       </c>
       <c r="O2" t="n">
-        <v>115031128035</v>
+        <v>116562871645</v>
       </c>
       <c r="P2" t="n">
         <v>25050</v>
@@ -626,16 +626,16 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>면역조절 펩타이드 장기지속형 제제 기술 특허 등록 소식에 품절주로 언급되며 목표가 상향 기대감.</t>
+          <t>삼익제약, 장기지속형 주사제 기술 특허 등록. 품절주 특성 속 목표가 30만 언급.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['면역조절', '펩타이드', '품절주']</t>
+          <t>['품절주', '장기지속형', '특허']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2880</v>
+        <v>2905</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+11.41%</t>
+          <t>'+12.38%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>1.34</v>
       </c>
       <c r="E3" t="n">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="F3" t="n">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="G3" t="n">
-        <v>122</v>
+        <v>139</v>
       </c>
       <c r="H3" t="n">
         <v>1.34</v>
@@ -702,7 +702,7 @@
         <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>60010983744</v>
+        <v>60714101359</v>
       </c>
       <c r="P3" t="n">
         <v>5100</v>
@@ -718,7 +718,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>594억 공급 계약 및 AI 관련 호재로 급등. 거래량 동반하며 신고가 경신 기대감 고조.</t>
+          <t>미국 기업과의 공급 계약 및 트럼프 AI 정책 관련 호재로 인한 5,000원 이상 상승 기대. 세계 최초 타이틀 보유.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
@@ -727,7 +727,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['공급 계약', 'AI', '급등']</t>
+          <t>['한국첨단소재', 'AI', '공급 계약']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -747,83 +747,83 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>JW신약</t>
+          <t>현대제철</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3690</v>
+        <v>35950</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+8.53%</t>
+          <t>'+8.94%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.12</v>
+        <v>-0.13</v>
       </c>
       <c r="E4" t="n">
-        <v>62</v>
+        <v>45</v>
       </c>
       <c r="F4" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="G4" t="n">
-        <v>153</v>
+        <v>196</v>
       </c>
       <c r="H4" t="n">
-        <v>0.83</v>
+        <v>14.93</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>3400</v>
+        <v>33000</v>
       </c>
       <c r="K4" t="n">
-        <v>3450</v>
+        <v>32750</v>
       </c>
       <c r="L4" t="n">
-        <v>4080</v>
+        <v>37200</v>
       </c>
       <c r="M4" t="n">
-        <v>3445</v>
+        <v>32750</v>
       </c>
       <c r="N4" t="n">
-        <v>0.71</v>
+        <v>15.06</v>
       </c>
       <c r="O4" t="n">
-        <v>131093277303</v>
+        <v>36244251800</v>
       </c>
       <c r="P4" t="n">
-        <v>4335</v>
+        <v>50400</v>
       </c>
       <c r="Q4" t="n">
-        <v>1246</v>
+        <v>23650</v>
       </c>
       <c r="R4" t="n">
-        <v>59000</v>
+        <v>126000</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>프로그램 매도 후 외국인 순매수 전환 및 4천원 안착 시도. 삼익제약과의 비교를 통한 대장주 경쟁.</t>
+          <t>저PBR 기업 정책에 따른 상승 기대감. 120일선 돌파 및 정배열 형성.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.1</v>
+        <v>0.5</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['외국인순매수', '프로그램', '단타']</t>
+          <t>['저PBR', '현대제철', '상승']</t>
         </is>
       </c>
       <c r="X4" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
@@ -832,38 +832,38 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>067290</t>
+          <t>004020</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>현대제철</t>
+          <t>광전자</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>36000</v>
+        <v>11100</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+7.14%</t>
+          <t>'+8.08%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>-0.13</v>
+        <v>0.26</v>
       </c>
       <c r="E5" t="n">
-        <v>45</v>
+        <v>114</v>
       </c>
       <c r="F5" t="n">
-        <v>42</v>
+        <v>81</v>
       </c>
       <c r="G5" t="n">
-        <v>174</v>
+        <v>298</v>
       </c>
       <c r="H5" t="n">
-        <v>14.93</v>
+        <v>17.93</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -871,51 +871,51 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>33600</v>
+        <v>10270</v>
       </c>
       <c r="K5" t="n">
+        <v>11000</v>
+      </c>
+      <c r="L5" t="n">
+        <v>11650</v>
+      </c>
+      <c r="M5" t="n">
+        <v>10010</v>
+      </c>
+      <c r="N5" t="n">
+        <v>17.67</v>
+      </c>
+      <c r="O5" t="n">
+        <v>270292008360</v>
+      </c>
+      <c r="P5" t="n">
+        <v>22450</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>1760</v>
+      </c>
+      <c r="R5" t="n">
+        <v>303000</v>
+      </c>
+      <c r="S5" t="n">
         <v>0</v>
       </c>
-      <c r="L5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" t="n">
-        <v>15.06</v>
-      </c>
-      <c r="O5" t="n">
-        <v>34765000000</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R5" t="n">
-        <v>126000</v>
-      </c>
-      <c r="S5" t="n">
-        <v>5000</v>
-      </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>저 PBR 기업으로 분류되어 상승 기대감 높음. 120일선 돌파 및 정배열 초기 국면 진입 분석.</t>
+          <t>AI 발전 기대감과 아이온큐 급등에 따른 긍정적 전망. 기타법인 매수세 유입.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['저PBR', '120일선', '정배열']</t>
+          <t>['AI', '아이온큐', '광통신']</t>
         </is>
       </c>
       <c r="X5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
@@ -924,77 +924,77 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>004020</t>
+          <t>017900</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>후성</t>
+          <t>JW신약</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>14750</v>
+        <v>3645</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+4.54%</t>
+          <t>'+7.21%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.06</v>
+        <v>0.12</v>
       </c>
       <c r="E6" t="n">
-        <v>43</v>
+        <v>64</v>
       </c>
       <c r="F6" t="n">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="G6" t="n">
-        <v>116</v>
+        <v>159</v>
       </c>
       <c r="H6" t="n">
-        <v>10.75</v>
+        <v>0.83</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>14110</v>
+        <v>3400</v>
       </c>
       <c r="K6" t="n">
-        <v>14110</v>
+        <v>3450</v>
       </c>
       <c r="L6" t="n">
-        <v>15250</v>
+        <v>4080</v>
       </c>
       <c r="M6" t="n">
-        <v>13400</v>
+        <v>3445</v>
       </c>
       <c r="N6" t="n">
-        <v>10.69</v>
+        <v>0.71</v>
       </c>
       <c r="O6" t="n">
-        <v>84366321390</v>
+        <v>132443521864</v>
       </c>
       <c r="P6" t="n">
-        <v>23550</v>
+        <v>4335</v>
       </c>
       <c r="Q6" t="n">
-        <v>5700</v>
+        <v>1246</v>
       </c>
       <c r="R6" t="n">
-        <v>-124000</v>
+        <v>59000</v>
       </c>
       <c r="S6" t="n">
-        <v>45000</v>
+        <v>0</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>15000원 돌파에 대한 기대감 속 공매도 세력 관련 언급. 거래량 증가 및 주가 변동성 나타남.</t>
+          <t>삼익제약과의 경쟁 속에서 대장주 역할 기대감. 프로그램 매매 및 외인 수급 변화 주시.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
@@ -1003,11 +1003,11 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['공매도', '거래량', '주가 변동성']</t>
+          <t>['JW신약', '삼익제약', '탈모']</t>
         </is>
       </c>
       <c r="X6" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
@@ -1016,77 +1016,77 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>093370</t>
+          <t>067290</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>SK이노베이션</t>
+          <t>HLB</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>142200</v>
+        <v>31700</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+4.02%</t>
+          <t>'+4.45%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.05</v>
+        <v>-0.05</v>
       </c>
       <c r="E7" t="n">
-        <v>106</v>
+        <v>99</v>
       </c>
       <c r="F7" t="n">
-        <v>57</v>
+        <v>77</v>
       </c>
       <c r="G7" t="n">
-        <v>230</v>
+        <v>499</v>
       </c>
       <c r="H7" t="n">
-        <v>15.81</v>
+        <v>17.5</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>136700</v>
+        <v>30350</v>
       </c>
       <c r="K7" t="n">
-        <v>139500</v>
+        <v>30250</v>
       </c>
       <c r="L7" t="n">
-        <v>144100</v>
+        <v>31700</v>
       </c>
       <c r="M7" t="n">
-        <v>138200</v>
+        <v>30250</v>
       </c>
       <c r="N7" t="n">
-        <v>15.76</v>
+        <v>17.55</v>
       </c>
       <c r="O7" t="n">
-        <v>75086924850</v>
+        <v>6879476300</v>
       </c>
       <c r="P7" t="n">
-        <v>164700</v>
+        <v>69200</v>
       </c>
       <c r="Q7" t="n">
-        <v>87700</v>
+        <v>24150</v>
       </c>
       <c r="R7" t="n">
-        <v>38000</v>
+        <v>19000</v>
       </c>
       <c r="S7" t="n">
-        <v>5000</v>
+        <v>0</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>정유 및 배터리 업황 호조에도 불구하고, 합병 관련 불확실성 및 기관/외인 매도세로 인한 하락.</t>
+          <t>담관암 신약 FDA 승인 기대감 속 유증 이슈 및 기관/외인 매도세로 인한 하락.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
@@ -1095,7 +1095,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['정유', '배터리', '합병']</t>
+          <t>['담관암', 'FDA승인', '유증']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1108,38 +1108,38 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>096770</t>
+          <t>028300</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>광전자</t>
+          <t>후성</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>10630</v>
+        <v>14650</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+3.51%</t>
+          <t>'+3.83%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.26</v>
+        <v>0.06</v>
       </c>
       <c r="E8" t="n">
-        <v>108</v>
+        <v>44</v>
       </c>
       <c r="F8" t="n">
-        <v>78</v>
+        <v>33</v>
       </c>
       <c r="G8" t="n">
-        <v>286</v>
+        <v>127</v>
       </c>
       <c r="H8" t="n">
-        <v>17.93</v>
+        <v>10.75</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1147,51 +1147,51 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>10270</v>
+        <v>14110</v>
       </c>
       <c r="K8" t="n">
-        <v>11000</v>
+        <v>14110</v>
       </c>
       <c r="L8" t="n">
-        <v>11650</v>
+        <v>15250</v>
       </c>
       <c r="M8" t="n">
-        <v>10010</v>
+        <v>13400</v>
       </c>
       <c r="N8" t="n">
-        <v>17.67</v>
+        <v>10.69</v>
       </c>
       <c r="O8" t="n">
-        <v>249171152935</v>
+        <v>87511920015</v>
       </c>
       <c r="P8" t="n">
-        <v>22450</v>
+        <v>23550</v>
       </c>
       <c r="Q8" t="n">
-        <v>1760</v>
+        <v>5700</v>
       </c>
       <c r="R8" t="n">
-        <v>303000</v>
+        <v>-124000</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>45000</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>트럼프 AI 정책 기대감 속 광통신 테마 상승. 아이온큐 프리마켓 급등 및 외인 매수세 유입.</t>
+          <t>15000원 돌파에 대한 기대감 속 공매도 세력 관련 언급. 거래량 증가 및 주가 변동성 나타남.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['광통신', 'AI', '아이온큐']</t>
+          <t>['공매도', '거래량', '주가 변동성']</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
@@ -1200,86 +1200,86 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>017900</t>
+          <t>093370</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>HLB</t>
+          <t>SK이노베이션</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>31400</v>
+        <v>141700</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+3.46%</t>
+          <t>'+3.66%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-0.05</v>
+        <v>0.05</v>
       </c>
       <c r="E9" t="n">
-        <v>93</v>
+        <v>113</v>
       </c>
       <c r="F9" t="n">
-        <v>75</v>
+        <v>63</v>
       </c>
       <c r="G9" t="n">
-        <v>491</v>
+        <v>237</v>
       </c>
       <c r="H9" t="n">
-        <v>17.5</v>
+        <v>15.81</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>30350</v>
+        <v>136700</v>
       </c>
       <c r="K9" t="n">
-        <v>30250</v>
+        <v>139500</v>
       </c>
       <c r="L9" t="n">
-        <v>31500</v>
+        <v>144100</v>
       </c>
       <c r="M9" t="n">
-        <v>30250</v>
+        <v>138200</v>
       </c>
       <c r="N9" t="n">
-        <v>17.55</v>
+        <v>15.76</v>
       </c>
       <c r="O9" t="n">
-        <v>5818211575</v>
+        <v>77378501850</v>
       </c>
       <c r="P9" t="n">
-        <v>69200</v>
+        <v>164700</v>
       </c>
       <c r="Q9" t="n">
-        <v>24150</v>
+        <v>87700</v>
       </c>
       <c r="R9" t="n">
-        <v>19000</v>
+        <v>38000</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>담관암 신약 FDA 승인 기대감 속 유증 이슈 및 기관/외인 매도세로 인한 하락.</t>
+          <t>합병 관련 불확실성 및 실적 우려 제기. 단기 급락 후 약반등 시도.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['담관암', 'FDA승인', '유증']</t>
+          <t>['합병', '영업이익', '정유']</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1292,90 +1292,90 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>028300</t>
+          <t>096770</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>샌즈랩</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1717000</v>
+        <v>6990</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+1.18%</t>
+          <t>'+1.30%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>-0.2</v>
+        <v>-0.97</v>
       </c>
       <c r="E10" t="n">
-        <v>800</v>
+        <v>40</v>
       </c>
       <c r="F10" t="n">
-        <v>458</v>
+        <v>26</v>
       </c>
       <c r="G10" t="n">
-        <v>1988</v>
+        <v>94</v>
       </c>
       <c r="H10" t="n">
-        <v>50.27</v>
+        <v>0.7</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>1697000</v>
+        <v>6900</v>
       </c>
       <c r="K10" t="n">
-        <v>1690000</v>
+        <v>7500</v>
       </c>
       <c r="L10" t="n">
-        <v>1725000</v>
+        <v>8190</v>
       </c>
       <c r="M10" t="n">
-        <v>1685000</v>
+        <v>6730</v>
       </c>
       <c r="N10" t="n">
-        <v>50.47</v>
+        <v>1.67</v>
       </c>
       <c r="O10" t="n">
-        <v>1591187822500</v>
+        <v>28015015175</v>
       </c>
       <c r="P10" t="n">
-        <v>2987000</v>
+        <v>10360</v>
       </c>
       <c r="Q10" t="n">
-        <v>325000</v>
+        <v>2965</v>
       </c>
       <c r="R10" t="n">
-        <v>-66000</v>
+        <v>35000</v>
       </c>
       <c r="S10" t="n">
-        <v>-53000</v>
+        <v>0</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>조정 마무리 및 상승 전환 기대감. 나스닥 선물 흐름 및 외인 매수세 유입 시 추가 상승 전망.</t>
+          <t>미국 보안주 강세와 함께 사이버 보안 테마로 엮이며, 미국 기업과 594억 공급계약 및 양자암호 관련 기대감.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['조정', '나스닥 선물', '외인 매수']</t>
+          <t>['사이버보안', '양자암호', '공급계약']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>71</v>
+        <v>2</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -1384,7 +1384,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>411080</t>
         </is>
       </c>
     </row>
@@ -1406,13 +1406,13 @@
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>60</v>
+        <v>69</v>
       </c>
       <c r="F11" t="n">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="G11" t="n">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="H11" t="n">
         <v>0.6</v>
@@ -1438,7 +1438,7 @@
         <v>0.6</v>
       </c>
       <c r="O11" t="n">
-        <v>138885087000</v>
+        <v>139755329065</v>
       </c>
       <c r="P11" t="n">
         <v>15960</v>
@@ -1454,7 +1454,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>주가 조작 의혹 및 공매도 관련 부정적 언급 다수. 신약 관련 기대감은 있으나 주가에 미반영.</t>
+          <t>주가 조작 및 공매도 관련 부정적 언급. 신약 기대감은 있으나 주가 움직임 답답.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
@@ -1483,31 +1483,31 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>샌즈랩</t>
+          <t>흥구석유</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>6950</v>
+        <v>14790</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'+0.72%</t>
+          <t>'+0.89%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>-0.97</v>
+        <v>-1.17</v>
       </c>
       <c r="E12" t="n">
-        <v>40</v>
+        <v>122</v>
       </c>
       <c r="F12" t="n">
-        <v>26</v>
+        <v>78</v>
       </c>
       <c r="G12" t="n">
-        <v>94</v>
+        <v>279</v>
       </c>
       <c r="H12" t="n">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1515,51 +1515,51 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>6900</v>
+        <v>14660</v>
       </c>
       <c r="K12" t="n">
-        <v>7500</v>
+        <v>14980</v>
       </c>
       <c r="L12" t="n">
-        <v>8190</v>
+        <v>15460</v>
       </c>
       <c r="M12" t="n">
-        <v>6730</v>
+        <v>14330</v>
       </c>
       <c r="N12" t="n">
-        <v>1.67</v>
+        <v>1.17</v>
       </c>
       <c r="O12" t="n">
-        <v>27803651910</v>
+        <v>35734321205</v>
       </c>
       <c r="P12" t="n">
-        <v>10360</v>
+        <v>36200</v>
       </c>
       <c r="Q12" t="n">
-        <v>2965</v>
+        <v>8920</v>
       </c>
       <c r="R12" t="n">
-        <v>35000</v>
+        <v>-47000</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>미국 보안주 강세와 함께 사이버 보안 테마로 엮이며, 미국 기업과 594억 공급계약 및 양자암호 관련 기대감.</t>
+          <t>이란발 국제유가 상승 기대감 속 주가 변동성. 투기적 흐름 경계.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['사이버보안', '양자암호', '공급계약']</t>
+          <t>['국제유가', '흥구석유', '투기']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
@@ -1568,38 +1568,38 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>411080</t>
+          <t>024060</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>250750</v>
+        <v>1704000</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'+0.70%</t>
+          <t>'+0.41%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.2</v>
       </c>
       <c r="E13" t="n">
         <v>800</v>
       </c>
       <c r="F13" t="n">
-        <v>470</v>
+        <v>466</v>
       </c>
       <c r="G13" t="n">
-        <v>2014</v>
+        <v>1963</v>
       </c>
       <c r="H13" t="n">
-        <v>46.57</v>
+        <v>50.27</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1607,38 +1607,38 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>249000</v>
+        <v>1697000</v>
       </c>
       <c r="K13" t="n">
-        <v>248000</v>
+        <v>1690000</v>
       </c>
       <c r="L13" t="n">
-        <v>252000</v>
+        <v>1725000</v>
       </c>
       <c r="M13" t="n">
-        <v>247500</v>
+        <v>1685000</v>
       </c>
       <c r="N13" t="n">
-        <v>46.64</v>
+        <v>50.47</v>
       </c>
       <c r="O13" t="n">
-        <v>881534155500</v>
+        <v>1705389225000</v>
       </c>
       <c r="P13" t="n">
-        <v>374500</v>
+        <v>2987000</v>
       </c>
       <c r="Q13" t="n">
-        <v>75900</v>
+        <v>325000</v>
       </c>
       <c r="R13" t="n">
-        <v>-156000</v>
+        <v>-66000</v>
       </c>
       <c r="S13" t="n">
-        <v>-305000</v>
+        <v>-53000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>AI 관련 기대감과 시장 안정에 대한 낙관론 존재. 그러나 정치적 이슈 및 반도체 시장 불안감으로 하락 전망도 공존.</t>
+          <t>나스닥 선물 및 코스피 야간 선물 흐름에 따른 상승 기대감. 외인 매수세 유입 시 긍정적 전망.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
@@ -1647,11 +1647,11 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['AI', '반도체', '시장 전망']</t>
+          <t>['반도체', 'SK하이닉스', '외인 매수']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>106</v>
+        <v>71</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
@@ -1660,38 +1660,38 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>18890</v>
+        <v>249500</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'+0.69%</t>
+          <t>'+0.20%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>-0.02</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="E14" t="n">
-        <v>46</v>
+        <v>800</v>
       </c>
       <c r="F14" t="n">
-        <v>31</v>
+        <v>468</v>
       </c>
       <c r="G14" t="n">
-        <v>190</v>
+        <v>1890</v>
       </c>
       <c r="H14" t="n">
-        <v>10.53</v>
+        <v>46.57</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1699,51 +1699,51 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>18760</v>
+        <v>249000</v>
       </c>
       <c r="K14" t="n">
-        <v>18440</v>
+        <v>248000</v>
       </c>
       <c r="L14" t="n">
-        <v>19060</v>
+        <v>252000</v>
       </c>
       <c r="M14" t="n">
-        <v>18120</v>
+        <v>247500</v>
       </c>
       <c r="N14" t="n">
-        <v>10.55</v>
+        <v>46.64</v>
       </c>
       <c r="O14" t="n">
-        <v>32106219130</v>
+        <v>968266468000</v>
       </c>
       <c r="P14" t="n">
-        <v>40350</v>
+        <v>374500</v>
       </c>
       <c r="Q14" t="n">
-        <v>3320</v>
+        <v>75900</v>
       </c>
       <c r="R14" t="n">
-        <v>69000</v>
+        <v>-156000</v>
       </c>
       <c r="S14" t="n">
-        <v>-6000</v>
+        <v>-305000</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>대차해지 운동 참여 독려 및 건설 대장주로서의 기대감 표출. 해외 건설 수주 가능성 언급.</t>
+          <t>시장 안정화 기대감과 함께 저가 매수 기회 언급. 정치적 이슈 관련 부정적 전망도 존재.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['대차해지', '해외건설', '건설 대장주']</t>
+          <t>['반도체', '저가 매수', '시장 안정']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>16</v>
+        <v>106</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
@@ -1752,90 +1752,90 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>흥구석유</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>14760</v>
+        <v>18790</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'+0.68%</t>
+          <t>'+0.16%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>-1.17</v>
+        <v>-0.02</v>
       </c>
       <c r="E15" t="n">
-        <v>122</v>
+        <v>49</v>
       </c>
       <c r="F15" t="n">
-        <v>78</v>
+        <v>31</v>
       </c>
       <c r="G15" t="n">
-        <v>278</v>
+        <v>199</v>
       </c>
       <c r="H15" t="n">
-        <v>0</v>
+        <v>10.53</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>14660</v>
+        <v>18760</v>
       </c>
       <c r="K15" t="n">
-        <v>14980</v>
+        <v>18440</v>
       </c>
       <c r="L15" t="n">
-        <v>15460</v>
+        <v>19060</v>
       </c>
       <c r="M15" t="n">
-        <v>14330</v>
+        <v>18120</v>
       </c>
       <c r="N15" t="n">
-        <v>1.17</v>
+        <v>10.55</v>
       </c>
       <c r="O15" t="n">
-        <v>35090998705</v>
+        <v>33711244020</v>
       </c>
       <c r="P15" t="n">
-        <v>36200</v>
+        <v>40350</v>
       </c>
       <c r="Q15" t="n">
-        <v>8920</v>
+        <v>3320</v>
       </c>
       <c r="R15" t="n">
-        <v>-47000</v>
+        <v>69000</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>-6000</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>국제 유가 상승 및 지정학적 리스크(이란, 후티 반군) 관련 언급과 함께 유가 하락 및 장난질에 대한 부정적 전망 혼재.</t>
+          <t>대차해지 운동 참여 독려 및 건설 대장주로서의 기대감 표출. 해외 건설 수주 가능성 언급.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['국제유가', '지정학적 리스크', '헤지주']</t>
+          <t>['대차해지', '해외건설', '건설 대장주']</t>
         </is>
       </c>
       <c r="X15" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
@@ -1844,7 +1844,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>024060</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
@@ -1855,24 +1855,24 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>225500</v>
+        <v>224500</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'+0.22%</t>
+          <t>'-0.22%</t>
         </is>
       </c>
       <c r="D16" t="n">
         <v>0.15</v>
       </c>
       <c r="E16" t="n">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="F16" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G16" t="n">
-        <v>566</v>
+        <v>585</v>
       </c>
       <c r="H16" t="n">
         <v>7.2</v>
@@ -1898,7 +1898,7 @@
         <v>7.05</v>
       </c>
       <c r="O16" t="n">
-        <v>59186575000</v>
+        <v>61481037750</v>
       </c>
       <c r="P16" t="n">
         <v>426000</v>
@@ -1943,83 +1943,83 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>LG디스플레이</t>
+          <t>빛과전자</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>8800</v>
+        <v>4305</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'-0.56%</t>
+          <t>'-0.46%</t>
         </is>
       </c>
       <c r="D17" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="E17" t="n">
+        <v>46</v>
+      </c>
+      <c r="F17" t="n">
+        <v>32</v>
+      </c>
+      <c r="G17" t="n">
+        <v>136</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="J17" t="n">
+        <v>4325</v>
+      </c>
+      <c r="K17" t="n">
+        <v>4325</v>
+      </c>
+      <c r="L17" t="n">
+        <v>4415</v>
+      </c>
+      <c r="M17" t="n">
+        <v>4050</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="O17" t="n">
+        <v>50662921047</v>
+      </c>
+      <c r="P17" t="n">
+        <v>8100</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>592</v>
+      </c>
+      <c r="R17" t="n">
+        <v>95000</v>
+      </c>
+      <c r="S17" t="n">
         <v>0</v>
       </c>
-      <c r="E17" t="n">
-        <v>68</v>
-      </c>
-      <c r="F17" t="n">
-        <v>39</v>
-      </c>
-      <c r="G17" t="n">
-        <v>212</v>
-      </c>
-      <c r="H17" t="n">
-        <v>27.16</v>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>MarketType.KOSPI</t>
-        </is>
-      </c>
-      <c r="J17" t="n">
-        <v>8850</v>
-      </c>
-      <c r="K17" t="n">
-        <v>8750</v>
-      </c>
-      <c r="L17" t="n">
-        <v>8840</v>
-      </c>
-      <c r="M17" t="n">
-        <v>8670</v>
-      </c>
-      <c r="N17" t="n">
-        <v>27.16</v>
-      </c>
-      <c r="O17" t="n">
-        <v>12912772655</v>
-      </c>
-      <c r="P17" t="n">
-        <v>17950</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>8120</v>
-      </c>
-      <c r="R17" t="n">
-        <v>-427000</v>
-      </c>
-      <c r="S17" t="n">
-        <v>-11000</v>
-      </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>목표 주가 하향 조정 및 연속 적자에 대한 비판. 삼성디스플레이와 비교하며 저평가 주장도 있으나 부정적 전망 우세.</t>
+          <t>삼성SDS와의 4381억 공급 계약 공시에도 불구하고 주가 움직임 답답. 광전자 대비 낮은 상승률.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['목표주가', '적자', '저평가']</t>
+          <t>['공급 계약', '빛과전자', '삼성SDS']</t>
         </is>
       </c>
       <c r="X17" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
@@ -2028,38 +2028,38 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>034220</t>
+          <t>069540</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>LG디스플레이</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>85800</v>
+        <v>8790</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'-1.38%</t>
+          <t>'-0.68%</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>-0.11</v>
+        <v>0</v>
       </c>
       <c r="E18" t="n">
-        <v>128</v>
+        <v>71</v>
       </c>
       <c r="F18" t="n">
-        <v>77</v>
+        <v>40</v>
       </c>
       <c r="G18" t="n">
-        <v>585</v>
+        <v>228</v>
       </c>
       <c r="H18" t="n">
-        <v>23.45</v>
+        <v>27.16</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -2067,51 +2067,51 @@
         </is>
       </c>
       <c r="J18" t="n">
-        <v>87000</v>
+        <v>8850</v>
       </c>
       <c r="K18" t="n">
-        <v>86200</v>
+        <v>8750</v>
       </c>
       <c r="L18" t="n">
-        <v>86700</v>
+        <v>8840</v>
       </c>
       <c r="M18" t="n">
-        <v>85000</v>
+        <v>8670</v>
       </c>
       <c r="N18" t="n">
-        <v>23.56</v>
+        <v>27.16</v>
       </c>
       <c r="O18" t="n">
-        <v>64340610700</v>
+        <v>13302107570</v>
       </c>
       <c r="P18" t="n">
-        <v>139200</v>
+        <v>17950</v>
       </c>
       <c r="Q18" t="n">
-        <v>57000</v>
+        <v>8120</v>
       </c>
       <c r="R18" t="n">
-        <v>-164000</v>
+        <v>-427000</v>
       </c>
       <c r="S18" t="n">
-        <v>-62000</v>
+        <v>-11000</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>원전 관련 ETF 출시 및 X에너지 급등에 따른 기대감 속에서, 전날 하락에 대한 반발 매수세 유입.</t>
+          <t>목표주가 하향 조정 및 적자 지속에 대한 부정적 전망. 삼성디스플레이와 비교하며 저평가 주장도 존재.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['원전', 'ETF', '에너지']</t>
+          <t>['목표주가', '적자', 'PBR']</t>
         </is>
       </c>
       <c r="X18" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
@@ -2120,7 +2120,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>034220</t>
         </is>
       </c>
     </row>
@@ -2131,24 +2131,24 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>14250</v>
+        <v>14350</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'-1.66%</t>
+          <t>'-0.97%</t>
         </is>
       </c>
       <c r="D19" t="n">
         <v>-0.08</v>
       </c>
       <c r="E19" t="n">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="F19" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G19" t="n">
-        <v>303</v>
+        <v>323</v>
       </c>
       <c r="H19" t="n">
         <v>1.8</v>
@@ -2174,7 +2174,7 @@
         <v>1.88</v>
       </c>
       <c r="O19" t="n">
-        <v>38650002930</v>
+        <v>40266931245</v>
       </c>
       <c r="P19" t="n">
         <v>31500</v>
@@ -2190,7 +2190,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>머니투데이 방송 홍보에도 불구하고 미증시 하락 및 AI, FOMC 등 거시경제 변수로 인한 보합세.</t>
+          <t>머니투데이 방송 홍보 언급 있으나, 대외 변수 및 주가 부진으로 인한 혼조세.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
@@ -2199,7 +2199,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['광통신', '외국인매수', 'AI']</t>
+          <t>['광통신', '외인매수', '변동성']</t>
         </is>
       </c>
       <c r="X19" t="n">
@@ -2219,83 +2219,83 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>빛과전자</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>4185</v>
+        <v>85600</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>'-3.24%</t>
+          <t>'-1.61%</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>0.18</v>
+        <v>-0.11</v>
       </c>
       <c r="E20" t="n">
-        <v>45</v>
+        <v>133</v>
       </c>
       <c r="F20" t="n">
-        <v>31</v>
+        <v>81</v>
       </c>
       <c r="G20" t="n">
-        <v>128</v>
+        <v>601</v>
       </c>
       <c r="H20" t="n">
-        <v>0.77</v>
+        <v>23.45</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J20" t="n">
-        <v>4325</v>
+        <v>87000</v>
       </c>
       <c r="K20" t="n">
-        <v>4325</v>
+        <v>86200</v>
       </c>
       <c r="L20" t="n">
-        <v>4415</v>
+        <v>86700</v>
       </c>
       <c r="M20" t="n">
-        <v>4050</v>
+        <v>85000</v>
       </c>
       <c r="N20" t="n">
-        <v>0.59</v>
+        <v>23.56</v>
       </c>
       <c r="O20" t="n">
-        <v>43758966217</v>
+        <v>67680255850</v>
       </c>
       <c r="P20" t="n">
-        <v>8100</v>
+        <v>139200</v>
       </c>
       <c r="Q20" t="n">
-        <v>592</v>
+        <v>57000</v>
       </c>
       <c r="R20" t="n">
-        <v>95000</v>
+        <v>-164000</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>-62000</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>삼성SDS와 4381억 공급계약 공시에도 불구하고 광통신 및 5G 테마 부진으로 인한 하락세.</t>
+          <t>원전 사업 기대감 및 엑스에너지 급등 동반. 단기적 주가 회복 및 상승 전망.</t>
         </is>
       </c>
       <c r="U20" t="inlineStr"/>
       <c r="V20" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>['공급계약', '광통신', '5G']</t>
+          <t>['원전', '두산에너빌리티', '엑스에너지']</t>
         </is>
       </c>
       <c r="X20" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
@@ -2304,7 +2304,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>069540</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
@@ -2315,24 +2315,24 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>21175</v>
+        <v>21100</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>'-4.19%</t>
+          <t>'-4.52%</t>
         </is>
       </c>
       <c r="D21" t="n">
         <v>0.09</v>
       </c>
       <c r="E21" t="n">
-        <v>91</v>
+        <v>103</v>
       </c>
       <c r="F21" t="n">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="G21" t="n">
-        <v>227</v>
+        <v>239</v>
       </c>
       <c r="H21" t="n">
         <v>28.9</v>
@@ -2352,13 +2352,13 @@
         <v>21850</v>
       </c>
       <c r="M21" t="n">
-        <v>21150</v>
+        <v>21050</v>
       </c>
       <c r="N21" t="n">
         <v>28.81</v>
       </c>
       <c r="O21" t="n">
-        <v>32312969075</v>
+        <v>35793166825</v>
       </c>
       <c r="P21" t="n">
         <v>35350</v>
@@ -2374,16 +2374,16 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>12억 달러 수주 공시에도 불구하고 주가 하락에 대한 불만 다수. 악성 루머 및 신뢰도 저하 언급.</t>
+          <t>12억 달러 수주 공시를 기반으로 한 상승 기대감. 금투, 투신, 연기금 매도 및 주포 악질 언급으로 부정적 전망.</t>
         </is>
       </c>
       <c r="U21" t="inlineStr"/>
       <c r="V21" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>['수주 공시', '주가 하락', '신뢰도']</t>
+          <t>['수주 공시', '조선주', '외인 매도']</t>
         </is>
       </c>
       <c r="X21" t="n">

--- a/data/trending_integrated_20260915_10.xlsx
+++ b/data/trending_integrated_20260915_10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z21"/>
+  <dimension ref="A1:Z23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -563,31 +563,31 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>삼익제약</t>
+          <t>원익홀딩스</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>10970</v>
+        <v>25750</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+18.34%</t>
+          <t>'+17.58%</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>-0.06</v>
+        <v>0.01</v>
       </c>
       <c r="E2" t="n">
-        <v>71</v>
+        <v>45</v>
       </c>
       <c r="F2" t="n">
-        <v>51</v>
+        <v>34</v>
       </c>
       <c r="G2" t="n">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H2" t="n">
-        <v>1.19</v>
+        <v>4.9</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -595,51 +595,51 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>9270</v>
+        <v>21900</v>
       </c>
       <c r="K2" t="n">
-        <v>9810</v>
+        <v>21700</v>
       </c>
       <c r="L2" t="n">
-        <v>12050</v>
+        <v>26750</v>
       </c>
       <c r="M2" t="n">
-        <v>9800</v>
+        <v>21500</v>
       </c>
       <c r="N2" t="n">
-        <v>1.25</v>
+        <v>4.89</v>
       </c>
       <c r="O2" t="n">
-        <v>116562871645</v>
+        <v>155845532925</v>
       </c>
       <c r="P2" t="n">
-        <v>25050</v>
+        <v>50600</v>
       </c>
       <c r="Q2" t="n">
-        <v>3705</v>
+        <v>10380</v>
       </c>
       <c r="R2" t="n">
-        <v>33000</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>삼익제약, 장기지속형 주사제 기술 특허 등록. 품절주 특성 속 목표가 30만 언급.</t>
+          <t>프로그램 매물 감소와 정배열 기대감 속에서 주가 상승 흐름이 좋으나, 뚜렷한 공시나 뉴스는 부재함.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.7</v>
+        <v>0.1</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['품절주', '장기지속형', '특허']</t>
+          <t>['정배열', '프로그램 매물', '공시']</t>
         </is>
       </c>
       <c r="X2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
@@ -648,38 +648,38 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>014950</t>
+          <t>030530</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>한국첨단소재</t>
+          <t>삼익제약</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2905</v>
+        <v>10840</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+12.38%</t>
+          <t>'+16.94%</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1.34</v>
+        <v>-0.06</v>
       </c>
       <c r="E3" t="n">
-        <v>55</v>
+        <v>75</v>
       </c>
       <c r="F3" t="n">
-        <v>36</v>
+        <v>54</v>
       </c>
       <c r="G3" t="n">
-        <v>139</v>
+        <v>88</v>
       </c>
       <c r="H3" t="n">
-        <v>1.34</v>
+        <v>1.19</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -687,51 +687,51 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>2585</v>
+        <v>9270</v>
       </c>
       <c r="K3" t="n">
-        <v>2725</v>
+        <v>9810</v>
       </c>
       <c r="L3" t="n">
-        <v>3200</v>
+        <v>12050</v>
       </c>
       <c r="M3" t="n">
-        <v>2690</v>
+        <v>9800</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="O3" t="n">
-        <v>60714101359</v>
+        <v>121351766470</v>
       </c>
       <c r="P3" t="n">
-        <v>5100</v>
+        <v>25050</v>
       </c>
       <c r="Q3" t="n">
-        <v>966</v>
+        <v>3705</v>
       </c>
       <c r="R3" t="n">
-        <v>-374000</v>
+        <v>33000</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>미국 기업과의 공급 계약 및 트럼프 AI 정책 관련 호재로 인한 5,000원 이상 상승 기대. 세계 최초 타이틀 보유.</t>
+          <t>면역조절 펩타이드 장기지속형 제제 기술 특허 등록 및 상한가. 유통 물량 적은 품절주.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['한국첨단소재', 'AI', '공급 계약']</t>
+          <t>['특허', '장기지속형', '품절주']</t>
         </is>
       </c>
       <c r="X3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
@@ -740,86 +740,86 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>062970</t>
+          <t>014950</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>현대제철</t>
+          <t>한국첨단소재</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>35950</v>
+        <v>2865</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+8.94%</t>
+          <t>'+10.83%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>-0.13</v>
+        <v>1.34</v>
       </c>
       <c r="E4" t="n">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="F4" t="n">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="G4" t="n">
-        <v>196</v>
+        <v>140</v>
       </c>
       <c r="H4" t="n">
-        <v>14.93</v>
+        <v>1.34</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>33000</v>
+        <v>2585</v>
       </c>
       <c r="K4" t="n">
-        <v>32750</v>
+        <v>2725</v>
       </c>
       <c r="L4" t="n">
-        <v>37200</v>
+        <v>3200</v>
       </c>
       <c r="M4" t="n">
-        <v>32750</v>
+        <v>2690</v>
       </c>
       <c r="N4" t="n">
-        <v>15.06</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>36244251800</v>
+        <v>61178362072</v>
       </c>
       <c r="P4" t="n">
-        <v>50400</v>
+        <v>5100</v>
       </c>
       <c r="Q4" t="n">
-        <v>23650</v>
+        <v>966</v>
       </c>
       <c r="R4" t="n">
-        <v>126000</v>
+        <v>-374000</v>
       </c>
       <c r="S4" t="n">
-        <v>5000</v>
+        <v>0</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>저PBR 기업 정책에 따른 상승 기대감. 120일선 돌파 및 정배열 형성.</t>
+          <t>미국 기업과 594억 공급 계약 및 세계 최초 타이틀. 트럼프 AI 발언에 따른 기대감 상승.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['저PBR', '현대제철', '상승']</t>
+          <t>['공급 계약', 'AI', '세계 최초']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -832,38 +832,38 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>004020</t>
+          <t>062970</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>광전자</t>
+          <t>두산퓨얼셀</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>11100</v>
+        <v>52600</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+8.08%</t>
+          <t>'+10.04%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.26</v>
+        <v>-0.18</v>
       </c>
       <c r="E5" t="n">
-        <v>114</v>
+        <v>58</v>
       </c>
       <c r="F5" t="n">
-        <v>81</v>
+        <v>43</v>
       </c>
       <c r="G5" t="n">
-        <v>298</v>
+        <v>132</v>
       </c>
       <c r="H5" t="n">
-        <v>17.93</v>
+        <v>13.97</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -871,51 +871,51 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>10270</v>
+        <v>47800</v>
       </c>
       <c r="K5" t="n">
-        <v>11000</v>
+        <v>47300</v>
       </c>
       <c r="L5" t="n">
-        <v>11650</v>
+        <v>54600</v>
       </c>
       <c r="M5" t="n">
-        <v>10010</v>
+        <v>46400</v>
       </c>
       <c r="N5" t="n">
-        <v>17.67</v>
+        <v>14.15</v>
       </c>
       <c r="O5" t="n">
-        <v>270292008360</v>
+        <v>50082030925</v>
       </c>
       <c r="P5" t="n">
-        <v>22450</v>
+        <v>108900</v>
       </c>
       <c r="Q5" t="n">
-        <v>1760</v>
+        <v>18230</v>
       </c>
       <c r="R5" t="n">
-        <v>303000</v>
+        <v>37000</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>3000</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>AI 발전 기대감과 아이온큐 급등에 따른 긍정적 전망. 기타법인 매수세 유입.</t>
+          <t>대형 계약 체결 및 수소법 시행 기대감. 외국인/기관 매도 속 개인 순매수, 경쟁사 주가 상승.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['AI', '아이온큐', '광통신']</t>
+          <t>['수소법', '계약 체결', '연료전지']</t>
         </is>
       </c>
       <c r="X5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
@@ -924,90 +924,90 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>017900</t>
+          <t>336260</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>JW신약</t>
+          <t>현대제철</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3645</v>
+        <v>35750</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+7.21%</t>
+          <t>'+8.33%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.12</v>
+        <v>-0.13</v>
       </c>
       <c r="E6" t="n">
-        <v>64</v>
+        <v>46</v>
       </c>
       <c r="F6" t="n">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="G6" t="n">
-        <v>159</v>
+        <v>210</v>
       </c>
       <c r="H6" t="n">
-        <v>0.83</v>
+        <v>14.93</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>3400</v>
+        <v>33000</v>
       </c>
       <c r="K6" t="n">
-        <v>3450</v>
+        <v>32750</v>
       </c>
       <c r="L6" t="n">
-        <v>4080</v>
+        <v>37200</v>
       </c>
       <c r="M6" t="n">
-        <v>3445</v>
+        <v>32750</v>
       </c>
       <c r="N6" t="n">
-        <v>0.71</v>
+        <v>15.06</v>
       </c>
       <c r="O6" t="n">
-        <v>132443521864</v>
+        <v>37436966125</v>
       </c>
       <c r="P6" t="n">
-        <v>4335</v>
+        <v>50400</v>
       </c>
       <c r="Q6" t="n">
-        <v>1246</v>
+        <v>23650</v>
       </c>
       <c r="R6" t="n">
-        <v>59000</v>
+        <v>126000</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>삼익제약과의 경쟁 속에서 대장주 역할 기대감. 프로그램 매매 및 외인 수급 변화 주시.</t>
+          <t>저PBR 기업 정책에 따른 상승 기대감. 120일선 돌파 및 정배열 형성.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['JW신약', '삼익제약', '탈모']</t>
+          <t>['저PBR', '현대제철', '상승']</t>
         </is>
       </c>
       <c r="X6" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
@@ -1016,38 +1016,38 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>067290</t>
+          <t>004020</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>HLB</t>
+          <t>JW신약</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>31700</v>
+        <v>3635</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+4.45%</t>
+          <t>'+6.91%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-0.05</v>
+        <v>0.12</v>
       </c>
       <c r="E7" t="n">
-        <v>99</v>
+        <v>64</v>
       </c>
       <c r="F7" t="n">
-        <v>77</v>
+        <v>38</v>
       </c>
       <c r="G7" t="n">
-        <v>499</v>
+        <v>164</v>
       </c>
       <c r="H7" t="n">
-        <v>17.5</v>
+        <v>0.83</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -1055,38 +1055,38 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>30350</v>
+        <v>3400</v>
       </c>
       <c r="K7" t="n">
-        <v>30250</v>
+        <v>3450</v>
       </c>
       <c r="L7" t="n">
-        <v>31700</v>
+        <v>4080</v>
       </c>
       <c r="M7" t="n">
-        <v>30250</v>
+        <v>3445</v>
       </c>
       <c r="N7" t="n">
-        <v>17.55</v>
+        <v>0.71</v>
       </c>
       <c r="O7" t="n">
-        <v>6879476300</v>
+        <v>133741043093</v>
       </c>
       <c r="P7" t="n">
-        <v>69200</v>
+        <v>4335</v>
       </c>
       <c r="Q7" t="n">
-        <v>24150</v>
+        <v>1246</v>
       </c>
       <c r="R7" t="n">
-        <v>19000</v>
+        <v>59000</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>담관암 신약 FDA 승인 기대감 속 유증 이슈 및 기관/외인 매도세로 인한 하락.</t>
+          <t>삼익제약과의 경쟁 구도 속에서 주가 변동성. 단기 트레이딩 관점 및 3700원 돌파 여부 주목.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
@@ -1095,11 +1095,11 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['담관암', 'FDA승인', '유증']</t>
+          <t>['단타', '삼익제약', '3700원']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -1108,38 +1108,38 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>028300</t>
+          <t>067290</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>후성</t>
+          <t>광전자</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>14650</v>
+        <v>10790</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+3.83%</t>
+          <t>'+5.06%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.06</v>
+        <v>0.26</v>
       </c>
       <c r="E8" t="n">
-        <v>44</v>
+        <v>126</v>
       </c>
       <c r="F8" t="n">
-        <v>33</v>
+        <v>87</v>
       </c>
       <c r="G8" t="n">
-        <v>127</v>
+        <v>311</v>
       </c>
       <c r="H8" t="n">
-        <v>10.75</v>
+        <v>17.93</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1147,51 +1147,51 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>14110</v>
+        <v>10270</v>
       </c>
       <c r="K8" t="n">
-        <v>14110</v>
+        <v>11000</v>
       </c>
       <c r="L8" t="n">
-        <v>15250</v>
+        <v>11650</v>
       </c>
       <c r="M8" t="n">
-        <v>13400</v>
+        <v>10010</v>
       </c>
       <c r="N8" t="n">
-        <v>10.69</v>
+        <v>17.67</v>
       </c>
       <c r="O8" t="n">
-        <v>87511920015</v>
+        <v>291175955740</v>
       </c>
       <c r="P8" t="n">
-        <v>23550</v>
+        <v>22450</v>
       </c>
       <c r="Q8" t="n">
-        <v>5700</v>
+        <v>1760</v>
       </c>
       <c r="R8" t="n">
-        <v>-124000</v>
+        <v>303000</v>
       </c>
       <c r="S8" t="n">
-        <v>45000</v>
+        <v>0</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>15000원 돌파에 대한 기대감 속 공매도 세력 관련 언급. 거래량 증가 및 주가 변동성 나타남.</t>
+          <t>미국 AI 및 광통신주 강세와 트럼프 발언에 따른 기대감. 기타 법인 매수세 유입.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['공매도', '거래량', '주가 변동성']</t>
+          <t>['광통신', 'AI', '트럼프']</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
@@ -1200,86 +1200,86 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>093370</t>
+          <t>017900</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>SK이노베이션</t>
+          <t>HLB</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>141700</v>
+        <v>31725</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+3.66%</t>
+          <t>'+4.53%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.05</v>
+        <v>-0.05</v>
       </c>
       <c r="E9" t="n">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="F9" t="n">
-        <v>63</v>
+        <v>81</v>
       </c>
       <c r="G9" t="n">
-        <v>237</v>
+        <v>526</v>
       </c>
       <c r="H9" t="n">
-        <v>15.81</v>
+        <v>17.5</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>136700</v>
+        <v>30350</v>
       </c>
       <c r="K9" t="n">
-        <v>139500</v>
+        <v>30250</v>
       </c>
       <c r="L9" t="n">
-        <v>144100</v>
+        <v>31800</v>
       </c>
       <c r="M9" t="n">
-        <v>138200</v>
+        <v>30250</v>
       </c>
       <c r="N9" t="n">
-        <v>15.76</v>
+        <v>17.55</v>
       </c>
       <c r="O9" t="n">
-        <v>77378501850</v>
+        <v>7292477625</v>
       </c>
       <c r="P9" t="n">
-        <v>164700</v>
+        <v>69200</v>
       </c>
       <c r="Q9" t="n">
-        <v>87700</v>
+        <v>24150</v>
       </c>
       <c r="R9" t="n">
-        <v>38000</v>
+        <v>19000</v>
       </c>
       <c r="S9" t="n">
-        <v>5000</v>
+        <v>0</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>합병 관련 불확실성 및 실적 우려 제기. 단기 급락 후 약반등 시도.</t>
+          <t>담관암 신약 FDA 승인 기대감 속 유증 이슈 및 기관/외인 매도세로 인한 하락.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['합병', '영업이익', '정유']</t>
+          <t>['담관암', 'FDA승인', '유증']</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1292,90 +1292,90 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>096770</t>
+          <t>028300</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>샌즈랩</t>
+          <t>후성</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>6990</v>
+        <v>14670</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+1.30%</t>
+          <t>'+3.97%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>-0.97</v>
+        <v>0.06</v>
       </c>
       <c r="E10" t="n">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="F10" t="n">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="G10" t="n">
-        <v>94</v>
+        <v>133</v>
       </c>
       <c r="H10" t="n">
-        <v>0.7</v>
+        <v>10.75</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>6900</v>
+        <v>14110</v>
       </c>
       <c r="K10" t="n">
-        <v>7500</v>
+        <v>14110</v>
       </c>
       <c r="L10" t="n">
-        <v>8190</v>
+        <v>15250</v>
       </c>
       <c r="M10" t="n">
-        <v>6730</v>
+        <v>13400</v>
       </c>
       <c r="N10" t="n">
-        <v>1.67</v>
+        <v>10.69</v>
       </c>
       <c r="O10" t="n">
-        <v>28015015175</v>
+        <v>89141295820</v>
       </c>
       <c r="P10" t="n">
-        <v>10360</v>
+        <v>23550</v>
       </c>
       <c r="Q10" t="n">
-        <v>2965</v>
+        <v>5700</v>
       </c>
       <c r="R10" t="n">
-        <v>35000</v>
+        <v>-124000</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>45000</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>미국 보안주 강세와 함께 사이버 보안 테마로 엮이며, 미국 기업과 594억 공급계약 및 양자암호 관련 기대감.</t>
+          <t>거래량 증가와 함께 15000원 돌파 시도, 주포 움직임에 대한 기대와 우려 혼재.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['사이버보안', '양자암호', '공급계약']</t>
+          <t>['주포', '거래량', '15000원']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -1384,38 +1384,38 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>411080</t>
+          <t>093370</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>현대약품</t>
+          <t>SK이노베이션</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>10100</v>
+        <v>141500</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'+1.10%</t>
+          <t>'+3.51%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="E11" t="n">
-        <v>69</v>
+        <v>117</v>
       </c>
       <c r="F11" t="n">
-        <v>37</v>
+        <v>65</v>
       </c>
       <c r="G11" t="n">
-        <v>74</v>
+        <v>244</v>
       </c>
       <c r="H11" t="n">
-        <v>0.6</v>
+        <v>15.81</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1423,47 +1423,47 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>9990</v>
+        <v>136700</v>
       </c>
       <c r="K11" t="n">
-        <v>10110</v>
+        <v>139500</v>
       </c>
       <c r="L11" t="n">
-        <v>11390</v>
+        <v>144100</v>
       </c>
       <c r="M11" t="n">
-        <v>10040</v>
+        <v>138200</v>
       </c>
       <c r="N11" t="n">
-        <v>0.6</v>
+        <v>15.76</v>
       </c>
       <c r="O11" t="n">
-        <v>139755329065</v>
+        <v>79472576300</v>
       </c>
       <c r="P11" t="n">
-        <v>15960</v>
+        <v>164700</v>
       </c>
       <c r="Q11" t="n">
-        <v>3500</v>
+        <v>87700</v>
       </c>
       <c r="R11" t="n">
-        <v>220000</v>
+        <v>38000</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>주가 조작 및 공매도 관련 부정적 언급. 신약 기대감은 있으나 주가 움직임 답답.</t>
+          <t>합병 관련 이슈와 주가 변동성에 대한 부정적 의견이 많으며, 실적 기대감 언급도 있으나 투자자들의 우려가 큼.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['주가 조작', '공매도', '신약']</t>
+          <t>['합병', '주가 변동성', '실적']</t>
         </is>
       </c>
       <c r="X11" t="n">
@@ -1476,90 +1476,90 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>004310</t>
+          <t>096770</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>흥구석유</t>
+          <t>현대약품</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>14790</v>
+        <v>10070</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'+0.89%</t>
+          <t>'+0.80%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>-1.17</v>
+        <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>122</v>
+        <v>72</v>
       </c>
       <c r="F12" t="n">
-        <v>78</v>
+        <v>38</v>
       </c>
       <c r="G12" t="n">
-        <v>279</v>
+        <v>79</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>14660</v>
+        <v>9990</v>
       </c>
       <c r="K12" t="n">
-        <v>14980</v>
+        <v>10110</v>
       </c>
       <c r="L12" t="n">
-        <v>15460</v>
+        <v>11390</v>
       </c>
       <c r="M12" t="n">
-        <v>14330</v>
+        <v>10040</v>
       </c>
       <c r="N12" t="n">
-        <v>1.17</v>
+        <v>0.6</v>
       </c>
       <c r="O12" t="n">
-        <v>35734321205</v>
+        <v>141238704900</v>
       </c>
       <c r="P12" t="n">
-        <v>36200</v>
+        <v>15960</v>
       </c>
       <c r="Q12" t="n">
-        <v>8920</v>
+        <v>3500</v>
       </c>
       <c r="R12" t="n">
-        <v>-47000</v>
+        <v>220000</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>이란발 국제유가 상승 기대감 속 주가 변동성. 투기적 흐름 경계.</t>
+          <t>주가 조작 및 공매도 관련 논란, 신약 개발 기대에도 불구하고 하락 압력.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['국제유가', '흥구석유', '투기']</t>
+          <t>['주가 조작', '공매도', '신약']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
@@ -1568,38 +1568,38 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>024060</t>
+          <t>004310</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1704000</v>
+        <v>18880</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'+0.41%</t>
+          <t>'+0.64%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>-0.2</v>
+        <v>-0.02</v>
       </c>
       <c r="E13" t="n">
-        <v>800</v>
+        <v>49</v>
       </c>
       <c r="F13" t="n">
-        <v>466</v>
+        <v>31</v>
       </c>
       <c r="G13" t="n">
-        <v>1963</v>
+        <v>205</v>
       </c>
       <c r="H13" t="n">
-        <v>50.27</v>
+        <v>10.53</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1607,51 +1607,51 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>1697000</v>
+        <v>18760</v>
       </c>
       <c r="K13" t="n">
-        <v>1690000</v>
+        <v>18440</v>
       </c>
       <c r="L13" t="n">
-        <v>1725000</v>
+        <v>19060</v>
       </c>
       <c r="M13" t="n">
-        <v>1685000</v>
+        <v>18120</v>
       </c>
       <c r="N13" t="n">
-        <v>50.47</v>
+        <v>10.55</v>
       </c>
       <c r="O13" t="n">
-        <v>1705389225000</v>
+        <v>34817541220</v>
       </c>
       <c r="P13" t="n">
-        <v>2987000</v>
+        <v>40350</v>
       </c>
       <c r="Q13" t="n">
-        <v>325000</v>
+        <v>3320</v>
       </c>
       <c r="R13" t="n">
-        <v>-66000</v>
+        <v>69000</v>
       </c>
       <c r="S13" t="n">
-        <v>-53000</v>
+        <v>-6000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>나스닥 선물 및 코스피 야간 선물 흐름에 따른 상승 기대감. 외인 매수세 유입 시 긍정적 전망.</t>
+          <t>대차해지 운동 참여 독려 및 건설 대장주로서의 기대감 표출. 해외 건설 수주 가능성 언급.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['반도체', 'SK하이닉스', '외인 매수']</t>
+          <t>['대차해지', '해외건설', '건설 대장주']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>71</v>
+        <v>16</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
@@ -1660,38 +1660,38 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>249500</v>
+        <v>1707000</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'+0.20%</t>
+          <t>'+0.59%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.2</v>
       </c>
       <c r="E14" t="n">
         <v>800</v>
       </c>
       <c r="F14" t="n">
-        <v>468</v>
+        <v>460</v>
       </c>
       <c r="G14" t="n">
-        <v>1890</v>
+        <v>1993</v>
       </c>
       <c r="H14" t="n">
-        <v>46.57</v>
+        <v>50.27</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1699,51 +1699,51 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>249000</v>
+        <v>1697000</v>
       </c>
       <c r="K14" t="n">
-        <v>248000</v>
+        <v>1690000</v>
       </c>
       <c r="L14" t="n">
-        <v>252000</v>
+        <v>1725000</v>
       </c>
       <c r="M14" t="n">
-        <v>247500</v>
+        <v>1685000</v>
       </c>
       <c r="N14" t="n">
-        <v>46.64</v>
+        <v>50.47</v>
       </c>
       <c r="O14" t="n">
-        <v>968266468000</v>
+        <v>1784626086500</v>
       </c>
       <c r="P14" t="n">
-        <v>374500</v>
+        <v>2987000</v>
       </c>
       <c r="Q14" t="n">
-        <v>75900</v>
+        <v>325000</v>
       </c>
       <c r="R14" t="n">
-        <v>-156000</v>
+        <v>-66000</v>
       </c>
       <c r="S14" t="n">
-        <v>-305000</v>
+        <v>-53000</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>시장 안정화 기대감과 함께 저가 매수 기회 언급. 정치적 이슈 관련 부정적 전망도 존재.</t>
+          <t>나스닥 선물 및 코스피 야간 선물 흐름에 따른 상승 기대감. 외인 매수세 유입 시 긍정적 전망.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['반도체', '저가 매수', '시장 안정']</t>
+          <t>['반도체', 'SK하이닉스', '외인 매수']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>106</v>
+        <v>71</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
@@ -1752,90 +1752,90 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>흥구석유</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>18790</v>
+        <v>14730</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'+0.16%</t>
+          <t>'+0.48%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>-0.02</v>
+        <v>-1.17</v>
       </c>
       <c r="E15" t="n">
-        <v>49</v>
+        <v>124</v>
       </c>
       <c r="F15" t="n">
-        <v>31</v>
+        <v>79</v>
       </c>
       <c r="G15" t="n">
-        <v>199</v>
+        <v>284</v>
       </c>
       <c r="H15" t="n">
-        <v>10.53</v>
+        <v>0</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>18760</v>
+        <v>14660</v>
       </c>
       <c r="K15" t="n">
-        <v>18440</v>
+        <v>14980</v>
       </c>
       <c r="L15" t="n">
-        <v>19060</v>
+        <v>15460</v>
       </c>
       <c r="M15" t="n">
-        <v>18120</v>
+        <v>14330</v>
       </c>
       <c r="N15" t="n">
-        <v>10.55</v>
+        <v>1.17</v>
       </c>
       <c r="O15" t="n">
-        <v>33711244020</v>
+        <v>36275256265</v>
       </c>
       <c r="P15" t="n">
-        <v>40350</v>
+        <v>36200</v>
       </c>
       <c r="Q15" t="n">
-        <v>3320</v>
+        <v>8920</v>
       </c>
       <c r="R15" t="n">
-        <v>69000</v>
+        <v>-47000</v>
       </c>
       <c r="S15" t="n">
-        <v>-6000</v>
+        <v>0</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>대차해지 운동 참여 독려 및 건설 대장주로서의 기대감 표출. 해외 건설 수주 가능성 언급.</t>
+          <t>국제 유가 상승 및 중동 관련 뉴스가 있으나, 주가 변동은 크지 않으며 개인 투자자들의 불안감이 혼재함.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['대차해지', '해외건설', '건설 대장주']</t>
+          <t>['국제 유가', '중동 정세', '개인 투자자']</t>
         </is>
       </c>
       <c r="X15" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
@@ -1844,38 +1844,38 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>024060</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>한미반도체</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>224500</v>
+        <v>249750</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'-0.22%</t>
+          <t>'+0.30%</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>0.15</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="E16" t="n">
-        <v>123</v>
+        <v>800</v>
       </c>
       <c r="F16" t="n">
-        <v>68</v>
+        <v>472</v>
       </c>
       <c r="G16" t="n">
-        <v>585</v>
+        <v>1808</v>
       </c>
       <c r="H16" t="n">
-        <v>7.2</v>
+        <v>46.57</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1883,51 +1883,51 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>225000</v>
+        <v>249000</v>
       </c>
       <c r="K16" t="n">
-        <v>228500</v>
+        <v>248000</v>
       </c>
       <c r="L16" t="n">
-        <v>229000</v>
+        <v>252000</v>
       </c>
       <c r="M16" t="n">
-        <v>219500</v>
+        <v>247500</v>
       </c>
       <c r="N16" t="n">
-        <v>7.05</v>
+        <v>46.64</v>
       </c>
       <c r="O16" t="n">
-        <v>61481037750</v>
+        <v>1020047799500</v>
       </c>
       <c r="P16" t="n">
-        <v>426000</v>
+        <v>374500</v>
       </c>
       <c r="Q16" t="n">
-        <v>89500</v>
+        <v>75900</v>
       </c>
       <c r="R16" t="n">
-        <v>-102000</v>
+        <v>-156000</v>
       </c>
       <c r="S16" t="n">
-        <v>-2000</v>
+        <v>-305000</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>머스크 테슬라의 테라팹에 패키징 장비 공급 단독 보도 및 이에 따른 기대감 형성. 공매도 세력에 대한 언급 및 반등 기대.</t>
+          <t>시장 안정 기대와 메모리 반도체 수요 긍정 전망. 정치적 이슈에 따른 변동성 우려.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0.8</v>
+        <v>0.2</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['테라팹', '패키징 장비', '공매도']</t>
+          <t>['메모리 반도체', 'AI', '시장']</t>
         </is>
       </c>
       <c r="X16" t="n">
-        <v>2</v>
+        <v>106</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
@@ -1936,90 +1936,90 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>042700</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>빛과전자</t>
+          <t>한미반도체</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>4305</v>
+        <v>225500</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'-0.46%</t>
+          <t>'+0.22%</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>0.18</v>
+        <v>0.15</v>
       </c>
       <c r="E17" t="n">
-        <v>46</v>
+        <v>125</v>
       </c>
       <c r="F17" t="n">
-        <v>32</v>
+        <v>69</v>
       </c>
       <c r="G17" t="n">
-        <v>136</v>
+        <v>596</v>
       </c>
       <c r="H17" t="n">
-        <v>0.77</v>
+        <v>7.2</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>4325</v>
+        <v>225000</v>
       </c>
       <c r="K17" t="n">
-        <v>4325</v>
+        <v>228500</v>
       </c>
       <c r="L17" t="n">
-        <v>4415</v>
+        <v>229000</v>
       </c>
       <c r="M17" t="n">
-        <v>4050</v>
+        <v>219500</v>
       </c>
       <c r="N17" t="n">
-        <v>0.59</v>
+        <v>7.05</v>
       </c>
       <c r="O17" t="n">
-        <v>50662921047</v>
+        <v>62786607750</v>
       </c>
       <c r="P17" t="n">
-        <v>8100</v>
+        <v>426000</v>
       </c>
       <c r="Q17" t="n">
-        <v>592</v>
+        <v>89500</v>
       </c>
       <c r="R17" t="n">
-        <v>95000</v>
+        <v>-102000</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>-2000</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>삼성SDS와의 4381억 공급 계약 공시에도 불구하고 주가 움직임 답답. 광전자 대비 낮은 상승률.</t>
+          <t>머스크 테슬라의 테라팹에 패키징 장비 공급 단독 보도 및 이에 따른 기대감 형성. 공매도 세력에 대한 언급 및 반등 기대.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0.3</v>
+        <v>0.8</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['공급 계약', '빛과전자', '삼성SDS']</t>
+          <t>['테라팹', '패키징 장비', '공매도']</t>
         </is>
       </c>
       <c r="X17" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
@@ -2028,90 +2028,90 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>069540</t>
+          <t>042700</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>LG디스플레이</t>
+          <t>샌즈랩</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>8790</v>
+        <v>6890</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'-0.68%</t>
+          <t>'-0.14%</t>
         </is>
       </c>
       <c r="D18" t="n">
+        <v>-0.97</v>
+      </c>
+      <c r="E18" t="n">
+        <v>41</v>
+      </c>
+      <c r="F18" t="n">
+        <v>26</v>
+      </c>
+      <c r="G18" t="n">
+        <v>94</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="J18" t="n">
+        <v>6900</v>
+      </c>
+      <c r="K18" t="n">
+        <v>7500</v>
+      </c>
+      <c r="L18" t="n">
+        <v>8190</v>
+      </c>
+      <c r="M18" t="n">
+        <v>6730</v>
+      </c>
+      <c r="N18" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="O18" t="n">
+        <v>28809116565</v>
+      </c>
+      <c r="P18" t="n">
+        <v>10360</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>2965</v>
+      </c>
+      <c r="R18" t="n">
+        <v>35000</v>
+      </c>
+      <c r="S18" t="n">
         <v>0</v>
       </c>
-      <c r="E18" t="n">
-        <v>71</v>
-      </c>
-      <c r="F18" t="n">
-        <v>40</v>
-      </c>
-      <c r="G18" t="n">
-        <v>228</v>
-      </c>
-      <c r="H18" t="n">
-        <v>27.16</v>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>MarketType.KOSPI</t>
-        </is>
-      </c>
-      <c r="J18" t="n">
-        <v>8850</v>
-      </c>
-      <c r="K18" t="n">
-        <v>8750</v>
-      </c>
-      <c r="L18" t="n">
-        <v>8840</v>
-      </c>
-      <c r="M18" t="n">
-        <v>8670</v>
-      </c>
-      <c r="N18" t="n">
-        <v>27.16</v>
-      </c>
-      <c r="O18" t="n">
-        <v>13302107570</v>
-      </c>
-      <c r="P18" t="n">
-        <v>17950</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>8120</v>
-      </c>
-      <c r="R18" t="n">
-        <v>-427000</v>
-      </c>
-      <c r="S18" t="n">
-        <v>-11000</v>
-      </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>목표주가 하향 조정 및 적자 지속에 대한 부정적 전망. 삼성디스플레이와 비교하며 저평가 주장도 존재.</t>
+          <t>미국 보안주 강세와 함께 사이버 보안 테마로 엮이며, 미국 기업과 594억 공급계약 및 양자암호 관련 기대감.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['목표주가', '적자', 'PBR']</t>
+          <t>['사이버보안', '양자암호', '공급계약']</t>
         </is>
       </c>
       <c r="X18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
@@ -2120,90 +2120,90 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>034220</t>
+          <t>411080</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>LG디스플레이</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>14350</v>
+        <v>8780</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'-0.97%</t>
+          <t>'-0.79%</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>-0.08</v>
+        <v>0</v>
       </c>
       <c r="E19" t="n">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="F19" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="G19" t="n">
-        <v>323</v>
+        <v>233</v>
       </c>
       <c r="H19" t="n">
-        <v>1.8</v>
+        <v>27.16</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>14490</v>
+        <v>8850</v>
       </c>
       <c r="K19" t="n">
-        <v>14410</v>
+        <v>8750</v>
       </c>
       <c r="L19" t="n">
-        <v>14600</v>
+        <v>8840</v>
       </c>
       <c r="M19" t="n">
-        <v>13930</v>
+        <v>8670</v>
       </c>
       <c r="N19" t="n">
-        <v>1.88</v>
+        <v>27.16</v>
       </c>
       <c r="O19" t="n">
-        <v>40266931245</v>
+        <v>13485435180</v>
       </c>
       <c r="P19" t="n">
-        <v>31500</v>
+        <v>17950</v>
       </c>
       <c r="Q19" t="n">
-        <v>1272</v>
+        <v>8120</v>
       </c>
       <c r="R19" t="n">
-        <v>6000</v>
+        <v>-427000</v>
       </c>
       <c r="S19" t="n">
-        <v>-9000</v>
+        <v>-11000</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>머니투데이 방송 홍보 언급 있으나, 대외 변수 및 주가 부진으로 인한 혼조세.</t>
+          <t>목표주가 하향 조정 및 적자 지속에 대한 부정적 전망. 삼성디스플레이와 비교하며 저평가 주장도 존재.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
       <c r="V19" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['광통신', '외인매수', '변동성']</t>
+          <t>['목표주가', '적자', 'PBR']</t>
         </is>
       </c>
       <c r="X19" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
@@ -2212,86 +2212,86 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>034220</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>85600</v>
+        <v>14250</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>'-1.61%</t>
+          <t>'-1.66%</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>-0.11</v>
+        <v>-0.08</v>
       </c>
       <c r="E20" t="n">
-        <v>133</v>
+        <v>74</v>
       </c>
       <c r="F20" t="n">
-        <v>81</v>
+        <v>46</v>
       </c>
       <c r="G20" t="n">
-        <v>601</v>
+        <v>333</v>
       </c>
       <c r="H20" t="n">
-        <v>23.45</v>
+        <v>1.8</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J20" t="n">
-        <v>87000</v>
+        <v>14490</v>
       </c>
       <c r="K20" t="n">
-        <v>86200</v>
+        <v>14410</v>
       </c>
       <c r="L20" t="n">
-        <v>86700</v>
+        <v>14600</v>
       </c>
       <c r="M20" t="n">
-        <v>85000</v>
+        <v>13930</v>
       </c>
       <c r="N20" t="n">
-        <v>23.56</v>
+        <v>1.88</v>
       </c>
       <c r="O20" t="n">
-        <v>67680255850</v>
+        <v>41878101145</v>
       </c>
       <c r="P20" t="n">
-        <v>139200</v>
+        <v>31500</v>
       </c>
       <c r="Q20" t="n">
-        <v>57000</v>
+        <v>1272</v>
       </c>
       <c r="R20" t="n">
-        <v>-164000</v>
+        <v>6000</v>
       </c>
       <c r="S20" t="n">
-        <v>-62000</v>
+        <v>-9000</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>원전 사업 기대감 및 엑스에너지 급등 동반. 단기적 주가 회복 및 상승 전망.</t>
+          <t>머니투데이 방송 언급 및 외인 매수 전환 등 긍정적 신호가 있으나, 금일 주가는 부진하며 불확실성이 존재함.</t>
         </is>
       </c>
       <c r="U20" t="inlineStr"/>
       <c r="V20" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>['원전', '두산에너빌리티', '엑스에너지']</t>
+          <t>['머니투데이', '외인 매수', '광통신']</t>
         </is>
       </c>
       <c r="X20" t="n">
@@ -2304,38 +2304,38 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>삼성중공업</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>21100</v>
+        <v>85500</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>'-4.52%</t>
+          <t>'-1.72%</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>0.09</v>
+        <v>-0.11</v>
       </c>
       <c r="E21" t="n">
-        <v>103</v>
+        <v>140</v>
       </c>
       <c r="F21" t="n">
-        <v>64</v>
+        <v>83</v>
       </c>
       <c r="G21" t="n">
-        <v>239</v>
+        <v>614</v>
       </c>
       <c r="H21" t="n">
-        <v>28.9</v>
+        <v>23.45</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -2343,58 +2343,242 @@
         </is>
       </c>
       <c r="J21" t="n">
-        <v>22100</v>
+        <v>87000</v>
       </c>
       <c r="K21" t="n">
-        <v>21850</v>
+        <v>86200</v>
       </c>
       <c r="L21" t="n">
-        <v>21850</v>
+        <v>86700</v>
       </c>
       <c r="M21" t="n">
-        <v>21050</v>
+        <v>85000</v>
       </c>
       <c r="N21" t="n">
-        <v>28.81</v>
+        <v>23.56</v>
       </c>
       <c r="O21" t="n">
-        <v>35793166825</v>
+        <v>70619163500</v>
       </c>
       <c r="P21" t="n">
-        <v>35350</v>
+        <v>139200</v>
       </c>
       <c r="Q21" t="n">
-        <v>18440</v>
+        <v>57000</v>
       </c>
       <c r="R21" t="n">
-        <v>-616000</v>
+        <v>-164000</v>
       </c>
       <c r="S21" t="n">
-        <v>-49000</v>
+        <v>-62000</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>12억 달러 수주 공시를 기반으로 한 상승 기대감. 금투, 투신, 연기금 매도 및 주포 악질 언급으로 부정적 전망.</t>
+          <t>원전 사업 및 에너지 독립 기대감과 함께 X에너지 상승 등 긍정적 뉴스가 있으나, 어제 주가 하락에 대한 언급도 있음.</t>
         </is>
       </c>
       <c r="U21" t="inlineStr"/>
       <c r="V21" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>['수주 공시', '조선주', '외인 매도']</t>
+          <t>['원전', '에너지 독립', 'X에너지']</t>
         </is>
       </c>
       <c r="X21" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>034020</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>빛과전자</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>4210</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>'-2.66%</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="E22" t="n">
+        <v>48</v>
+      </c>
+      <c r="F22" t="n">
+        <v>34</v>
+      </c>
+      <c r="G22" t="n">
+        <v>141</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="J22" t="n">
+        <v>4325</v>
+      </c>
+      <c r="K22" t="n">
+        <v>4325</v>
+      </c>
+      <c r="L22" t="n">
+        <v>4415</v>
+      </c>
+      <c r="M22" t="n">
+        <v>4050</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="O22" t="n">
+        <v>55378122170</v>
+      </c>
+      <c r="P22" t="n">
+        <v>8100</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>592</v>
+      </c>
+      <c r="R22" t="n">
+        <v>95000</v>
+      </c>
+      <c r="S22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>삼성SDS와 4381억 공급 계약 체결. 광전자 대비 낮은 상승률 및 매물대 부담.</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr"/>
+      <c r="V22" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>['공급 계약', '광전자', '매물대']</t>
+        </is>
+      </c>
+      <c r="X22" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>069540</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>삼성중공업</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>21000</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>'-4.98%</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="E23" t="n">
+        <v>115</v>
+      </c>
+      <c r="F23" t="n">
+        <v>68</v>
+      </c>
+      <c r="G23" t="n">
+        <v>265</v>
+      </c>
+      <c r="H23" t="n">
+        <v>28.9</v>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J23" t="n">
+        <v>22100</v>
+      </c>
+      <c r="K23" t="n">
+        <v>21850</v>
+      </c>
+      <c r="L23" t="n">
+        <v>21850</v>
+      </c>
+      <c r="M23" t="n">
+        <v>21000</v>
+      </c>
+      <c r="N23" t="n">
+        <v>28.81</v>
+      </c>
+      <c r="O23" t="n">
+        <v>38247066175</v>
+      </c>
+      <c r="P23" t="n">
+        <v>35350</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>18440</v>
+      </c>
+      <c r="R23" t="n">
+        <v>-616000</v>
+      </c>
+      <c r="S23" t="n">
+        <v>-49000</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>12억 달러 수주 공시에도 불구하고 주가 하락. 시장의 악재 해석 및 불확실성 지속.</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr"/>
+      <c r="V23" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>['수주 공시', '조선주', '악재']</t>
+        </is>
+      </c>
+      <c r="X23" t="n">
         <v>2</v>
       </c>
-      <c r="Y21" t="inlineStr">
+      <c r="Y23" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
+      <c r="Z23" t="inlineStr">
         <is>
           <t>010140</t>
         </is>
